--- a/cleaning_pipeline_R/neotree_scripts/mwi-scripts/NeoDischarge KCH - metadata.xlsx
+++ b/cleaning_pipeline_R/neotree_scripts/mwi-scripts/NeoDischarge KCH - metadata.xlsx
@@ -1100,7 +1100,7 @@
         <v>BirthWeight</v>
       </c>
       <c r="G11" t="str">
-        <v>Birth weight (g)</v>
+        <v>Birth Weight (g)</v>
       </c>
       <c r="H11" t="str">
         <v>number</v>
@@ -1393,7 +1393,7 @@
         <v>$NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24'</v>
       </c>
       <c r="N15" t="str">
-        <v>[{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AN","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AP","valueLabel":"Apnea","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ASP","valueLabel":"Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BA","valueLabel":"Birth Asphyxia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BO","valueLabel":"Bowel Obstruction","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BR","valueLabel":"Bronchiolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Cong","valueLabel":"Congenital abnormality incompatible with life","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CHD","valueLabel":"Congenital Heart Disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FO","valueLabel":"Fluid Overload","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GA","valueLabel":"Gastroenteritis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYPG","valueLabel":"Hypoglycaermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYPT","valueLabel":"Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYP","valueLabel":"Hypoxia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low Birth Weight","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MAL","valueLabel":"Malnutrition","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MA","valueLabel":"Meconium Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MEN","valueLabel":"Meningitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NEC","valueLabel":"Necrotising Enterocolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"EONS","valueLabel":"Neonatal Sepsis - Early Onset (EONS)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LONS","valueLabel":"Neonatal Sepsis - Late Onset (LONS)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NT","valueLabel":"Neonatal Tetenus","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PRRDS","valueLabel":"Prematurity with RDS","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PN","valueLabel":"Pneumonia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RDNT","valueLabel":"Respiratory distress of newborn (Term)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RF","valueLabel":"Respiratory Failure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SH","valueLabel":"Shock","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AN","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AP","valueLabel":"Apnea","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ASP","valueLabel":"Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BA","valueLabel":"Birth Asphyxia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BO","valueLabel":"Bowel Obstruction","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BR","valueLabel":"Bronchiolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Cong","valueLabel":"Congenital abnormality incompatible with life","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CHD","valueLabel":"Congenital Heart Disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FO","valueLabel":"Fluid Overload","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GA","valueLabel":"Gastroenteritis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYPG","valueLabel":"Hypoglycaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYPT","valueLabel":"Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYP","valueLabel":"Hypoxia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low Birth Weight","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MAL","valueLabel":"Malnutrition","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MA","valueLabel":"Meconium Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MEN","valueLabel":"Meningitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NEC","valueLabel":"Necrotising Enterocolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"EONS","valueLabel":"Neonatal Sepsis - Early Onset (EONS)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LONS","valueLabel":"Neonatal Sepsis - Late Onset (LONS)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NT","valueLabel":"Neonatal Tetenus","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PRRDS","valueLabel":"Prematurity with RDS","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PN","valueLabel":"Pneumonia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RDNT","valueLabel":"Respiratory distress of newborn (Term)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RF","valueLabel":"Respiratory Failure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SH","valueLabel":"Shock","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O15" t="str">
         <v>$NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24'</v>
@@ -1529,7 +1529,7 @@
         <v>$NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24'</v>
       </c>
       <c r="N17" t="str">
-        <v>[{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AN","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AP","valueLabel":"Apnea","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AS","valueLabel":"Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BDN","valueLabel":"Bleeding Disorder of the Newborn","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BO","valueLabel":"Bowel Obstruction","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CHD","valueLabel":"Congenital Heart Disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DEHY","valueLabel":"Dehydration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ELIM","valueLabel":"Electrolyte Imbalance","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"G","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GA","valueLabel":"Gastroenteritis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYGL","valueLabel":"Hypoglycemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYP","valueLabel":"Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIE","valueLabel":"Hypoxic Ischaemic Encephalopathy (HIE)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low Birth Weight","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MA","valueLabel":"Meconium Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MAL","valueLabel":"Malnutrition","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NEC","valueLabel":"Necrotising Enterocolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NS","valueLabel":"Neonatal sepsis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NT","valueLabel":"Neonatal Tetenus","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PRRDS","valueLabel":"Prematurity with RDS","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RDS","valueLabel":"Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PN","valueLabel":"Pneumonia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AN","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AP","valueLabel":"Apnea","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AS","valueLabel":"Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BDN","valueLabel":"Bleeding Disorder of the Newborn","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BO","valueLabel":"Bowel Obstruction","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CHD","valueLabel":"Congenital Heart Disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DEHY","valueLabel":"Dehydration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ELIM","valueLabel":"Electrolyte Imbalance","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"G","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GA","valueLabel":"Gastroenteritis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYP","valueLabel":"Hypoglycaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYP","valueLabel":"Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIE","valueLabel":"Hypoxic Ischaemic Encephalopathy (HIE)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low Birth Weight","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MA","valueLabel":"Meconium Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MAL","valueLabel":"Malnutrition","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NEC","valueLabel":"Necrotising Enterocolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NS","valueLabel":"Neonatal sepsis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NT","valueLabel":"Neonatal Tetenus","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PRRDS","valueLabel":"Prematurity with RDS","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RDS","valueLabel":"Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PN","valueLabel":"Pneumonia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O17" t="str">
         <v>$NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24'</v>
@@ -1644,7 +1644,7 @@
         <v>UIDBID</v>
       </c>
       <c r="G19" t="str">
-        <v xml:space="preserve">BID - ID number </v>
+        <v>BID - ID number</v>
       </c>
       <c r="H19" t="str">
         <v>string</v>
@@ -1712,7 +1712,7 @@
         <v>DateTimeAdmission</v>
       </c>
       <c r="G20" t="str">
-        <v xml:space="preserve">Date/time admission </v>
+        <v>Date/time admission</v>
       </c>
       <c r="H20" t="str">
         <v>datetime</v>
@@ -1869,7 +1869,7 @@
         <v/>
       </c>
       <c r="N22" t="str">
-        <v>[{"value":"STB","valueLabel":"Stillbirth - born dead at &gt; 28 wks"},{"value":"PND","valueLabel":"Born alive at &gt; 28 wks but dead on arrival"},{"value":"AB","valueLabel":"Abortion - born dead at &lt; 28 wks"},{"value":"DU","valueLabel":"Dumped Baby"}]</v>
+        <v>[{"value":"STB","valueLabel":"Stillbirth - born dead at &gt; 28 wks"},{"value":"PND","valueLabel":"Born alive at &gt; 28 wks but dead on arrival to Ethel"},{"value":"AB","valueLabel":"Abortion - born dead at &lt; 28 wks"},{"value":"DU","valueLabel":"Dumped Baby"}]</v>
       </c>
       <c r="O22" t="str">
         <v>$NeoTreeOutcome = 'BID'</v>
@@ -1996,7 +1996,7 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="L24" t="str">
         <v>No</v>
@@ -2120,7 +2120,7 @@
         <v>ModeDelivery</v>
       </c>
       <c r="G26" t="str">
-        <v>Mode of delivery</v>
+        <v>Mode of Delivery</v>
       </c>
       <c r="H26" t="str">
         <v>dropdown</v>
@@ -2392,7 +2392,7 @@
         <v>DateDischVitals</v>
       </c>
       <c r="G30" t="str">
-        <v xml:space="preserve">Date and Time of last recorded Vital Signs </v>
+        <v>Date and Time of last recorded Vital Signs</v>
       </c>
       <c r="H30" t="str">
         <v>datetime</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="N37" t="str">
-        <v>[{"value":"AB","valueLabel":"Abscess"},{"value":"An","valueLabel":"Anaemia"},{"value":"AL","valueLabel":"Albinism"},{"value":"Apn","valueLabel":"Apnoea of prematurity"},{"value":"BA","valueLabel":"Birth Asphyxia/HIE"},{"value":"BI","valueLabel":"Birth Injury"},{"value":"BDN","valueLabel":"Bleeding Disorder of a Newborn"},{"value":"BC","valueLabel":"Blood Clotting Disorder"},{"value":"BO","valueLabel":"Bowel Obstruction"},{"value":"BRON","valueLabel":"Bronchiolitis"},{"value":"CEP","valueLabel":"Cephalohematoma"},{"value":"Cong","valueLabel":"Congenital Abnormality"},{"value":"CS","valueLabel":"Congenital Syphillis"},{"value":"CHD","valueLabel":"Congenital Heart Disease"},{"value":"DWT","valueLabel":"Down Sydrome/Trisomy 21"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"FTT","valueLabel":"Failure to Thrive"},{"value":"GAN","valueLabel":"Gangrene"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"HYP","valueLabel":"Hypoglycemia"},{"value":"HIVX","valueLabel":"HIV Exposed"},{"value":"J","valueLabel":"Jaundice"},{"value":"LA","valueLabel":"Laryngomalacia"},{"value":"LBW","valueLabel":"Low Birth Weight"},{"value":"HBW","valueLabel":"High Birth Weight (&gt;4000g at birth)"},{"value":"MA","valueLabel":"Possible Meconium Aspiration"},{"value":"MD","valueLabel":"Musculoskeletal Abnormalities"},{"value":"NEC","valueLabel":"Necrotising Enterocolitis"},{"value":"EONS","valueLabel":"Neonatal Sepsis - Early Onset (EONS)"},{"value":"LONS","valueLabel":"Neonatal Sepsis - Late Onset (LONS)"},{"value":"NSepNC","valueLabel":"Risk factors for sepsis (but sepsis ruled out)"},{"value":"NT","valueLabel":"Neonatal Tetenus"},{"value":"MA","valueLabel":"Possible Meconium Aspiration"},{"value":"OT","valueLabel":"Oral Thrush"},{"value":"OPNE","valueLabel":"Opthalmia Neonatolum"},{"value":"NB","valueLabel":"Normal Baby"},{"value":"PR","valueLabel":"Prematurity"},{"value":"PremRD","valueLabel":"Prematurity with Respiratory Distress"},{"value":"PS","valueLabel":"Prune Belly Syndrome"},{"value":"PN","valueLabel":"Pneumonia"},{"value":"TermRD","valueLabel":"Term baby with Respiratory Distress"},{"value":"SKI","valueLabel":"Skin Infection"},{"value":"SEB","valueLabel":"Syphillis Exposed Baby"},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)"},{"value":"TR13","valueLabel":"Trisomy 13"},{"value":"OSC","valueLabel":"Other Surgical Conditions"},{"value":"OTH","valueLabel":"Other"}]</v>
+        <v>[{"value":"AB","valueLabel":"Abscess"},{"value":"An","valueLabel":"Anaemia"},{"value":"AL","valueLabel":"Albinism"},{"value":"Apn","valueLabel":"Apnoea of prematurity"},{"value":"BA","valueLabel":"Birth Asphyxia/HIE"},{"value":"BI","valueLabel":"Birth Injury"},{"value":"BDN","valueLabel":"Bleeding Disorder of a Newborn"},{"value":"BC","valueLabel":"Blood Clotting Disorder"},{"value":"BO","valueLabel":"Bowel Obstruction"},{"value":"BRON","valueLabel":"Bronchiolitis"},{"value":"CEP","valueLabel":"Cephalohematoma"},{"value":"Cong","valueLabel":"Congenital Abnormality"},{"value":"CS","valueLabel":"Congenital Syphillis"},{"value":"CHD","valueLabel":"Congenital Heart Disease"},{"value":"DWT","valueLabel":"Down Sydrome/Trisomy 21"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"FTT","valueLabel":"Failure to Thrive"},{"value":"GAN","valueLabel":"Gangrene"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"HYP","valueLabel":"Hypoglycaemia"},{"value":"HIVX","valueLabel":"HIV Exposed"},{"value":"J","valueLabel":"Jaundice"},{"value":"LA","valueLabel":"Laryngomalacia"},{"value":"LBW","valueLabel":"Low Birth Weight"},{"value":"HBW","valueLabel":"High Birth Weight (&gt;4000g at birth)"},{"value":"MA","valueLabel":"Possible Meconium Aspiration"},{"value":"MD","valueLabel":"Musculoskeletal Abnormalities"},{"value":"NEC","valueLabel":"Necrotising Enterocolitis"},{"value":"EONS","valueLabel":"Neonatal Sepsis - Early Onset (EONS)"},{"value":"LONS","valueLabel":"Neonatal Sepsis - Late Onset (LONS)"},{"value":"NSepNC","valueLabel":"Risk factors for sepsis (but sepsis ruled out)"},{"value":"NT","valueLabel":"Neonatal Tetenus"},{"value":"MA","valueLabel":"Possible Meconium Aspiration"},{"value":"OT","valueLabel":"Oral Thrush"},{"value":"OPNE","valueLabel":"Opthalmia Neonatolum"},{"value":"NB","valueLabel":"Normal Baby"},{"value":"PR","valueLabel":"Prematurity"},{"value":"PremRD","valueLabel":"Prematurity with Respiratory Distress"},{"value":"PS","valueLabel":"Prune Belly Syndrome"},{"value":"PN","valueLabel":"Pneumonia"},{"value":"TermRD","valueLabel":"Term baby with Respiratory Distress"},{"value":"SKI","valueLabel":"Skin Infection"},{"value":"SEB","valueLabel":"Syphillis Exposed Baby"},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)"},{"value":"TR13","valueLabel":"Trisomy 13"},{"value":"OSC","valueLabel":"Other Surgical Conditions"},{"value":"OTH","valueLabel":"Other"}]</v>
       </c>
       <c r="O37" t="str">
         <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'ABS' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'DCR' or $NeoTreeOutcome  = 'DPC'</v>
@@ -3208,7 +3208,7 @@
         <v>OtherProbsOth</v>
       </c>
       <c r="G42" t="str">
-        <v xml:space="preserve">If other what? </v>
+        <v>If other what?</v>
       </c>
       <c r="H42" t="str">
         <v>string</v>
@@ -3480,19 +3480,19 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C46" t="str">
-        <v>BIRTH HISTORY</v>
+        <v>RESPIRATORY SUPPORT</v>
       </c>
       <c r="D46" t="str">
-        <v>Resus</v>
+        <v>RESP SUPP</v>
       </c>
       <c r="E46" t="str">
         <v>multi_select</v>
       </c>
       <c r="F46" t="str">
-        <v>Resus</v>
+        <v>RESPSUP</v>
       </c>
       <c r="G46" t="str">
-        <v>Resuscitation given</v>
+        <v>Respiratory support received</v>
       </c>
       <c r="H46" t="str">
         <v>multi_select_option</v>
@@ -3510,13 +3510,13 @@
         <v>No</v>
       </c>
       <c r="M46" t="str">
-        <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'ABS' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24' or $NeoTreeOutcome = 'DCR' or $NeoTreeOutcome = 'DPC'</v>
+        <v xml:space="preserve">$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'ABS' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'NND&lt;24' or$NeoTreeOutcome = 'NND&gt;24' </v>
       </c>
       <c r="N46" t="str">
-        <v>[{"value":"Stim","valueLabel":"Stimulation","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Suc","valueLabel":"Suctioning","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O2","valueLabel":"Oxygen","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BVM","valueLabel":"Bag Valve Mask Ventilation (BVM)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CPR","valueLabel":"Cardio Pulmonary Resuscitation (CPR)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
+        <v>[{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"INO2","valueLabel":"Intra-Nasal Oxygen","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NCO2","valueLabel":"Nasal Cannulae Oxygen","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CPAP","valueLabel":"CPAP","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FM","valueLabel":"Face Mask Oxygen","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O46" t="str">
-        <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'ABS' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24' or $NeoTreeOutcome = 'DCR' or $NeoTreeOutcome = 'DPC'</v>
+        <v xml:space="preserve">$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'ABS' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'NND&lt;24' or$NeoTreeOutcome = 'NND&gt;24' </v>
       </c>
       <c r="P46" t="str">
         <v/>
@@ -3548,22 +3548,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C47" t="str">
-        <v>BIRTH HISTORY</v>
+        <v>DATE WEANED</v>
       </c>
       <c r="D47" t="str">
-        <v>Resus Length</v>
+        <v>DATE WEANED</v>
       </c>
       <c r="E47" t="str">
         <v>form</v>
       </c>
       <c r="F47" t="str">
-        <v>LengthResusKnown</v>
+        <v>DateWeaned</v>
       </c>
       <c r="G47" t="str">
-        <v>Length of resuscitation known?</v>
+        <v>Date weaned off resp support</v>
       </c>
       <c r="H47" t="str">
-        <v>dropdown</v>
+        <v>date</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -3581,10 +3581,10 @@
         <v/>
       </c>
       <c r="N47" t="str">
-        <v>[{"value":"Kn","valueLabel":"Known"},{"value":"Unk","valueLabel":"Unknown"}]</v>
+        <v/>
       </c>
       <c r="O47" t="str">
-        <v>$Resus = 'O2' or $Resus = 'BVM' or $Resus = 'CPR'</v>
+        <v>($NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO') and ($RESPSUP = 'INO2' or $RESPSUP = 'NCO2' or $RESPSUP = 'CPAP' or $RESPSUP = 'HB')</v>
       </c>
       <c r="P47" t="str">
         <v/>
@@ -3616,22 +3616,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C48" t="str">
-        <v>BIRTH HISTORY</v>
+        <v>PHOTOTHERAPY</v>
       </c>
       <c r="D48" t="str">
-        <v>Resus Length</v>
+        <v>PhotoTx</v>
       </c>
       <c r="E48" t="str">
-        <v>form</v>
+        <v>yesno</v>
       </c>
       <c r="F48" t="str">
-        <v>LengthResus</v>
+        <v>PHOTOTHERAPY</v>
       </c>
       <c r="G48" t="str">
-        <v>Length of resus (min)</v>
+        <v>Did baby receive phototherapy?</v>
       </c>
       <c r="H48" t="str">
-        <v>number</v>
+        <v>boolean</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -3646,13 +3646,13 @@
         <v>No</v>
       </c>
       <c r="M48" t="str">
-        <v>$LengthResusKnown = 'Kn'</v>
+        <v xml:space="preserve">$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'ABS' or $NeoTreeOutome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24' </v>
       </c>
       <c r="N48" t="str">
-        <v/>
+        <v>[{"value":"true","valueLabel":"Yes"},{"value":"false","valueLabel":"No"}]</v>
       </c>
       <c r="O48" t="str">
-        <v>$Resus = 'O2' or $Resus = 'BVM' or $Resus = 'CPR'</v>
+        <v xml:space="preserve">$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'ABS' or $NeoTreeOutome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24' </v>
       </c>
       <c r="P48" t="str">
         <v/>
@@ -3684,19 +3684,19 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C49" t="str">
-        <v>RESPIRATORY SUPPORT</v>
+        <v>MEDICATIONS GIVEN</v>
       </c>
       <c r="D49" t="str">
-        <v>RESP SUPP</v>
+        <v>MEDS</v>
       </c>
       <c r="E49" t="str">
         <v>multi_select</v>
       </c>
       <c r="F49" t="str">
-        <v>RESPSUP</v>
+        <v>MedsGiven</v>
       </c>
       <c r="G49" t="str">
-        <v>Respiratory support received</v>
+        <v>Medications given during admission</v>
       </c>
       <c r="H49" t="str">
         <v>multi_select_option</v>
@@ -3714,13 +3714,13 @@
         <v>No</v>
       </c>
       <c r="M49" t="str">
-        <v xml:space="preserve">$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'ABS' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'NND&lt;24' or$NeoTreeOutcome = 'NND&gt;24' </v>
+        <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'ABS' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24' or $NeoTreeOutcome = 'DCR' or $NeoTreeOutcome = 'DPC'</v>
       </c>
       <c r="N49" t="str">
-        <v>[{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"INO2","valueLabel":"Intra-Nasal Oxygen","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NCO2","valueLabel":"Nasal Cannulae Oxygen","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CPAP","valueLabel":"CPAP","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FM","valueLabel":"Face Mask Oxygen","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"BP","valueLabel":"X penicillin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GENT","valueLabel":"Gentamicin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CEF","valueLabel":"Ceftriaxone","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CHLX","valueLabel":"Chlorhexidine (for cord care)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PCM","valueLabel":"PCM","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AM","valueLabel":"Aminophylline","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NVP","valueLabel":"Nevirapine","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PHEN","valueLabel":"Phenobarbitone","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"VitK","valueLabel":"Vitamin K","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TEO","valueLabel":"Tetracycline Eye Ointment","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AMOX","valueLabel":"Amoxicillin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FLU","valueLabel":"Flucloxacillin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IMI","valueLabel":"Imipenam","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MET","valueLabel":"Metronidazole","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mero","valueLabel":"Meropenam","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AZT","valueLabel":"AZT (Zidovudine)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BCG","valueLabel":"BCG vaccine","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTV","valueLabel":"Tetanus Vaccine","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O49" t="str">
-        <v xml:space="preserve">$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'ABS' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'NND&lt;24' or$NeoTreeOutcome = 'NND&gt;24' </v>
+        <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'ABS' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24' or $NeoTreeOutcome = 'DCR' or $NeoTreeOutcome = 'DPC'</v>
       </c>
       <c r="P49" t="str">
         <v/>
@@ -3752,22 +3752,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C50" t="str">
-        <v>DATE WEANED</v>
+        <v>OTHER MEDICATIONS</v>
       </c>
       <c r="D50" t="str">
-        <v>DATE WEANED</v>
+        <v>Other Medication</v>
       </c>
       <c r="E50" t="str">
         <v>form</v>
       </c>
       <c r="F50" t="str">
-        <v>DateWeaned</v>
+        <v>MEDOTH</v>
       </c>
       <c r="G50" t="str">
-        <v>Date weaned off resp support</v>
+        <v>If other medications then what?</v>
       </c>
       <c r="H50" t="str">
-        <v>date</v>
+        <v>string</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -3788,7 +3788,7 @@
         <v/>
       </c>
       <c r="O50" t="str">
-        <v>($NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO') and ($RESPSUP = 'INO2' or $RESPSUP = 'NCO2' or $RESPSUP = 'CPAP' or $RESPSUP = 'HB')</v>
+        <v>$MedsGiven = 'OTH'</v>
       </c>
       <c r="P50" t="str">
         <v/>
@@ -3820,22 +3820,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C51" t="str">
-        <v>PHOTOTHERAPY</v>
+        <v>REVIEW</v>
       </c>
       <c r="D51" t="str">
-        <v>PhotoTx</v>
+        <v>Follow up</v>
       </c>
       <c r="E51" t="str">
-        <v>yesno</v>
+        <v>form</v>
       </c>
       <c r="F51" t="str">
-        <v>PHOTOTHERAPY</v>
+        <v>CLIN</v>
       </c>
       <c r="G51" t="str">
-        <v>Did baby receive phototherapy?</v>
+        <v>How many clinics have been organised for this baby?</v>
       </c>
       <c r="H51" t="str">
-        <v>boolean</v>
+        <v>dropdown</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -3850,13 +3850,13 @@
         <v>No</v>
       </c>
       <c r="M51" t="str">
-        <v xml:space="preserve">$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'ABS' or $NeoTreeOutome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24' </v>
+        <v/>
       </c>
       <c r="N51" t="str">
-        <v>[{"value":"true","valueLabel":"Yes"},{"value":"false","valueLabel":"No"}]</v>
+        <v>[{"value":"1","valueLabel":"One"},{"value":"2","valueLabel":"Two"},{"value":"3","valueLabel":"Three"},{"value":"Norm","valueLabel":"None"}]</v>
       </c>
       <c r="O51" t="str">
-        <v xml:space="preserve">$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'ABS' or $NeoTreeOutome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24' </v>
+        <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'DCR' or $NeoTreeOutcome = 'DPC'</v>
       </c>
       <c r="P51" t="str">
         <v/>
@@ -3888,22 +3888,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C52" t="str">
-        <v>MEDICATIONS GIVEN</v>
+        <v>REVIEW</v>
       </c>
       <c r="D52" t="str">
-        <v>MEDS</v>
+        <v>Follow up</v>
       </c>
       <c r="E52" t="str">
-        <v>multi_select</v>
+        <v>form</v>
       </c>
       <c r="F52" t="str">
-        <v>MedsGiven</v>
+        <v>CLIN1</v>
       </c>
       <c r="G52" t="str">
-        <v>Medications given during admission</v>
+        <v>Clinic 1 type?</v>
       </c>
       <c r="H52" t="str">
-        <v>multi_select_option</v>
+        <v>dropdown</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -3918,13 +3918,13 @@
         <v>No</v>
       </c>
       <c r="M52" t="str">
-        <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'ABS' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24' or $NeoTreeOutcome = 'DCR' or $NeoTreeOutcome = 'DPC'</v>
+        <v>$CLIN = '1' or $CLIN = '2' or $CLIN = '3'</v>
       </c>
       <c r="N52" t="str">
-        <v>[{"value":"BP","valueLabel":"X penicillin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GENT","valueLabel":"Gentamicin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CEF","valueLabel":"Ceftriaxone","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CHLX","valueLabel":"Chlorhexidine (for cord care)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PCM","valueLabel":"PCM","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AM","valueLabel":"Aminophylline","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NVP","valueLabel":"Nevirapine","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PHEN","valueLabel":"Phenobarbitone","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"VitK","valueLabel":"Vitamin K","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TEO","valueLabel":"Tetracycline Eye Ointment","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AMOX","valueLabel":"Amoxicillin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FLU","valueLabel":"Flucloxacillin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IMI","valueLabel":"Imipenam","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MET","valueLabel":"Metronidazole","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mero","valueLabel":"Meropenam","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AZT","valueLabel":"AZT (Zidovudine)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BCG","valueLabel":"BCG vaccine","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTV","valueLabel":"Tetanus Vaccine","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
+        <v>[{"value":"KMC","valueLabel":"Thursday KMC clinic on Ethel (KCH)"},{"value":"SURG","valueLabel":"Paeds Surgical Clinic (KCH)"},{"value":"NEURO","valueLabel":"Paeds Neuro Clinic (KCH)"},{"value":"Card","valueLabel":"Cardiac Clinic (KCH)"},{"value":"HC","valueLabel":"Health Centre follow up"},{"value":"PHY","valueLabel":"Physio"},{"value":"SEPS","valueLabel":"Sepsis follow up clinic"},{"value":"OTH","valueLabel":"Other"}]</v>
       </c>
       <c r="O52" t="str">
-        <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'ABS' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24' or $NeoTreeOutcome = 'DCR' or $NeoTreeOutcome = 'DPC'</v>
+        <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'DCR' or $NeoTreeOutcome = 'DPC'</v>
       </c>
       <c r="P52" t="str">
         <v/>
@@ -3956,19 +3956,19 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C53" t="str">
-        <v>OTHER MEDICATIONS</v>
+        <v>REVIEW</v>
       </c>
       <c r="D53" t="str">
-        <v>Other Medication</v>
+        <v>Follow up</v>
       </c>
       <c r="E53" t="str">
         <v>form</v>
       </c>
       <c r="F53" t="str">
-        <v>MEDOTH</v>
+        <v>CLIN1OTH</v>
       </c>
       <c r="G53" t="str">
-        <v>If other medications then what?</v>
+        <v>If other clinic 1 where?</v>
       </c>
       <c r="H53" t="str">
         <v>string</v>
@@ -3986,13 +3986,13 @@
         <v>No</v>
       </c>
       <c r="M53" t="str">
-        <v/>
+        <v>$CLIN1 = 'OTH'</v>
       </c>
       <c r="N53" t="str">
         <v/>
       </c>
       <c r="O53" t="str">
-        <v>$MedsGiven = 'OTH'</v>
+        <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'DCR' or $NeoTreeOutcome = 'DPC'</v>
       </c>
       <c r="P53" t="str">
         <v/>
@@ -4033,13 +4033,13 @@
         <v>form</v>
       </c>
       <c r="F54" t="str">
-        <v>CLIN</v>
+        <v>CLIN1DAT</v>
       </c>
       <c r="G54" t="str">
-        <v>How many clinics have been organised for this baby?</v>
+        <v>Date of review clinic 1 (DD/MM/YYYY)</v>
       </c>
       <c r="H54" t="str">
-        <v>dropdown</v>
+        <v>date</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -4054,10 +4054,10 @@
         <v>No</v>
       </c>
       <c r="M54" t="str">
-        <v/>
+        <v>$CLIN = '1' or $CLIN = '2' or $CLIN = '3'</v>
       </c>
       <c r="N54" t="str">
-        <v>[{"value":"1","valueLabel":"One"},{"value":"2","valueLabel":"Two"},{"value":"3","valueLabel":"Three"},{"value":"Norm","valueLabel":"None"}]</v>
+        <v/>
       </c>
       <c r="O54" t="str">
         <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'DCR' or $NeoTreeOutcome = 'DPC'</v>
@@ -4101,10 +4101,10 @@
         <v>form</v>
       </c>
       <c r="F55" t="str">
-        <v>CLIN1</v>
+        <v>CLIN2</v>
       </c>
       <c r="G55" t="str">
-        <v>Clinic 1 type?</v>
+        <v>Clinic 2 type?</v>
       </c>
       <c r="H55" t="str">
         <v>dropdown</v>
@@ -4122,7 +4122,7 @@
         <v>No</v>
       </c>
       <c r="M55" t="str">
-        <v>$CLIN = '1' or $CLIN = '2' or $CLIN = '3'</v>
+        <v>$CLIN = '2' or $CLIN = '3'</v>
       </c>
       <c r="N55" t="str">
         <v>[{"value":"KMC","valueLabel":"Thursday KMC clinic on Ethel (KCH)"},{"value":"SURG","valueLabel":"Paeds Surgical Clinic (KCH)"},{"value":"NEURO","valueLabel":"Paeds Neuro Clinic (KCH)"},{"value":"Card","valueLabel":"Cardiac Clinic (KCH)"},{"value":"HC","valueLabel":"Health Centre follow up"},{"value":"PHY","valueLabel":"Physio"},{"value":"SEPS","valueLabel":"Sepsis follow up clinic"},{"value":"OTH","valueLabel":"Other"}]</v>
@@ -4169,10 +4169,10 @@
         <v>form</v>
       </c>
       <c r="F56" t="str">
-        <v>CLIN1OTH</v>
+        <v>CLIN2OTH</v>
       </c>
       <c r="G56" t="str">
-        <v>If other clinic 1 where?</v>
+        <v>If other clinic 2 where?</v>
       </c>
       <c r="H56" t="str">
         <v>string</v>
@@ -4190,7 +4190,7 @@
         <v>No</v>
       </c>
       <c r="M56" t="str">
-        <v>$CLIN1 = 'OTH'</v>
+        <v>$CLIN2 = 'OTH'</v>
       </c>
       <c r="N56" t="str">
         <v/>
@@ -4237,10 +4237,10 @@
         <v>form</v>
       </c>
       <c r="F57" t="str">
-        <v>CLIN1DAT</v>
+        <v>CLIN2DAT</v>
       </c>
       <c r="G57" t="str">
-        <v>Date of review clinic 1 (DD/MM/YYYY)</v>
+        <v>Date of review clinic 2 (DD/MM/YYYY)</v>
       </c>
       <c r="H57" t="str">
         <v>date</v>
@@ -4258,7 +4258,7 @@
         <v>No</v>
       </c>
       <c r="M57" t="str">
-        <v>$CLIN = '1' or $CLIN = '2' or $CLIN = '3'</v>
+        <v>$CLIN = '2' or $CLIN = '3'</v>
       </c>
       <c r="N57" t="str">
         <v/>
@@ -4305,10 +4305,10 @@
         <v>form</v>
       </c>
       <c r="F58" t="str">
-        <v>CLIN2</v>
+        <v>CLIN3</v>
       </c>
       <c r="G58" t="str">
-        <v>Clinic 2 type?</v>
+        <v>Clinic 3 type?</v>
       </c>
       <c r="H58" t="str">
         <v>dropdown</v>
@@ -4326,7 +4326,7 @@
         <v>No</v>
       </c>
       <c r="M58" t="str">
-        <v>$CLIN = '2' or $CLIN = '3'</v>
+        <v>$CLIN = '3'</v>
       </c>
       <c r="N58" t="str">
         <v>[{"value":"KMC","valueLabel":"Thursday KMC clinic on Ethel (KCH)"},{"value":"SURG","valueLabel":"Paeds Surgical Clinic (KCH)"},{"value":"NEURO","valueLabel":"Paeds Neuro Clinic (KCH)"},{"value":"Card","valueLabel":"Cardiac Clinic (KCH)"},{"value":"HC","valueLabel":"Health Centre follow up"},{"value":"PHY","valueLabel":"Physio"},{"value":"SEPS","valueLabel":"Sepsis follow up clinic"},{"value":"OTH","valueLabel":"Other"}]</v>
@@ -4373,10 +4373,10 @@
         <v>form</v>
       </c>
       <c r="F59" t="str">
-        <v>CLIN2OTH</v>
+        <v>CLIN3OTH</v>
       </c>
       <c r="G59" t="str">
-        <v>If other clinic 2 where?</v>
+        <v>If other clinic 3 where?</v>
       </c>
       <c r="H59" t="str">
         <v>string</v>
@@ -4394,7 +4394,7 @@
         <v>No</v>
       </c>
       <c r="M59" t="str">
-        <v>$CLIN2 = 'OTH'</v>
+        <v>$CLIN3 = 'OTH'</v>
       </c>
       <c r="N59" t="str">
         <v/>
@@ -4441,10 +4441,10 @@
         <v>form</v>
       </c>
       <c r="F60" t="str">
-        <v>CLIN2DAT</v>
+        <v>CLIN3DAT</v>
       </c>
       <c r="G60" t="str">
-        <v xml:space="preserve">Date of review clinic 2 (DD/MM/YYYY)	</v>
+        <v>Date of review clinic 3 (DD/MM/YYYY)</v>
       </c>
       <c r="H60" t="str">
         <v>date</v>
@@ -4462,7 +4462,7 @@
         <v>No</v>
       </c>
       <c r="M60" t="str">
-        <v>$CLIN = '2' or $CLIN = '3'</v>
+        <v>$CLIN = '3'</v>
       </c>
       <c r="N60" t="str">
         <v/>
@@ -4500,22 +4500,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C61" t="str">
-        <v>REVIEW</v>
+        <v>Health Education</v>
       </c>
       <c r="D61" t="str">
-        <v>Follow up</v>
+        <v>Health Ed</v>
       </c>
       <c r="E61" t="str">
-        <v>form</v>
+        <v>management</v>
       </c>
       <c r="F61" t="str">
-        <v>CLIN3</v>
+        <v/>
       </c>
       <c r="G61" t="str">
-        <v>Clinic 3 type?</v>
+        <v/>
       </c>
       <c r="H61" t="str">
-        <v>dropdown</v>
+        <v/>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -4524,16 +4524,16 @@
         <v/>
       </c>
       <c r="K61" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="L61" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="M61" t="str">
-        <v>$CLIN = '3'</v>
+        <v/>
       </c>
       <c r="N61" t="str">
-        <v>[{"value":"KMC","valueLabel":"Thursday KMC clinic on Ethel (KCH)"},{"value":"SURG","valueLabel":"Paeds Surgical Clinic (KCH)"},{"value":"NEURO","valueLabel":"Paeds Neuro Clinic (KCH)"},{"value":"Card","valueLabel":"Cardiac Clinic (KCH)"},{"value":"HC","valueLabel":"Health Centre follow up"},{"value":"PHY","valueLabel":"Physio"},{"value":"SEPS","valueLabel":"Sepsis follow up clinic"},{"value":"OTH","valueLabel":"Other"}]</v>
+        <v/>
       </c>
       <c r="O61" t="str">
         <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'DCR' or $NeoTreeOutcome = 'DPC'</v>
@@ -4557,7 +4557,7 @@
         <v/>
       </c>
       <c r="V61" t="str">
-        <v/>
+        <v>{"actionText":"Health Education","contentText":"Please educate the mother on:","infoText":"","title":"Health Education","title1":"DANGER SIGNS","title2":"GENERAL EDUCATION","title3":"","title4":"","text1":"- Jaundice\n- Convulsions\n- Not able to breast feed\n- Difficulties in breathing\n- Lethargic\n- Fever\n- Hypothermia\n- Abdominal distention\n- Bleeding from the cord and what to do if any","text2":"- Immunisation\n- Family planning\n- Hygiene\n- Keeping baby warm\n- Malaria Prevention","text3":"","instructions":"","instructions2":"","instructions3":"","instructions4":"","notes":"","refKey":"","images":{"contentTextImage":null,"image1":null,"image2":null,"image3":null}}</v>
       </c>
     </row>
     <row r="62">
@@ -4568,22 +4568,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C62" t="str">
-        <v>REVIEW</v>
+        <v>Health Education/ Insecticide Net</v>
       </c>
       <c r="D62" t="str">
-        <v>Follow up</v>
+        <v>Health Ed/ ITN given</v>
       </c>
       <c r="E62" t="str">
         <v>form</v>
       </c>
       <c r="F62" t="str">
-        <v>CLIN3OTH</v>
+        <v>HealthEd</v>
       </c>
       <c r="G62" t="str">
-        <v>If other clinic 3 where?</v>
+        <v>Has Health Education been given to mother?</v>
       </c>
       <c r="H62" t="str">
-        <v>string</v>
+        <v>dropdown</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -4598,13 +4598,13 @@
         <v>No</v>
       </c>
       <c r="M62" t="str">
-        <v>$CLIN3 = 'OTH'</v>
+        <v/>
       </c>
       <c r="N62" t="str">
-        <v/>
+        <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"NO"}]</v>
       </c>
       <c r="O62" t="str">
-        <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'DCR' or $NeoTreeOutcome = 'DPC'</v>
+        <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO'</v>
       </c>
       <c r="P62" t="str">
         <v/>
@@ -4636,22 +4636,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C63" t="str">
-        <v>REVIEW</v>
+        <v>Health Education/ Insecticide Net</v>
       </c>
       <c r="D63" t="str">
-        <v>Follow up</v>
+        <v>Health Ed/ ITN given</v>
       </c>
       <c r="E63" t="str">
         <v>form</v>
       </c>
       <c r="F63" t="str">
-        <v>CLIN3DAT</v>
+        <v>ITN</v>
       </c>
       <c r="G63" t="str">
-        <v xml:space="preserve">Date of review clinic 3 (DD/MM/YYYY)	</v>
+        <v>Has the mother been given an Insecticide Treated Net?</v>
       </c>
       <c r="H63" t="str">
-        <v>date</v>
+        <v>dropdown</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -4666,13 +4666,13 @@
         <v>No</v>
       </c>
       <c r="M63" t="str">
-        <v>$CLIN = '3'</v>
+        <v/>
       </c>
       <c r="N63" t="str">
-        <v/>
+        <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"}]</v>
       </c>
       <c r="O63" t="str">
-        <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'DCR' or $NeoTreeOutcome = 'DPC'</v>
+        <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO'</v>
       </c>
       <c r="P63" t="str">
         <v/>
@@ -4704,22 +4704,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C64" t="str">
-        <v>Health Education</v>
+        <v>Modifiable Factors</v>
       </c>
       <c r="D64" t="str">
-        <v>Health Ed</v>
+        <v>Modifiable</v>
       </c>
       <c r="E64" t="str">
-        <v>management</v>
+        <v>form</v>
       </c>
       <c r="F64" t="str">
-        <v/>
+        <v>ModFactor1</v>
       </c>
       <c r="G64" t="str">
-        <v/>
+        <v>Modifiable factor 1</v>
       </c>
       <c r="H64" t="str">
-        <v/>
+        <v>string</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -4728,10 +4728,10 @@
         <v/>
       </c>
       <c r="K64" t="str">
-        <v/>
+        <v>No</v>
       </c>
       <c r="L64" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="M64" t="str">
         <v/>
@@ -4740,7 +4740,7 @@
         <v/>
       </c>
       <c r="O64" t="str">
-        <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'DCR' or $NeoTreeOutcome = 'DPC'</v>
+        <v>$NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24' or $NeoTreeOutcome = 'BID'</v>
       </c>
       <c r="P64" t="str">
         <v/>
@@ -4761,7 +4761,7 @@
         <v/>
       </c>
       <c r="V64" t="str">
-        <v>{"actionText":"Health Education","contentText":"Please educate the mother on:","infoText":"","title":"Health Education","title1":"DANGER SIGNS","title2":"GENERAL EDUCATION","title3":"","title4":"","text1":"- Jaundice\n- Convulsions\n- Not able to breast feed\n- Difficulties in breathing\n- Lethargic\n- Fever\n- Hypothermia\n- Abdominal distention\n- Bleeding from the cord and what to do if any","text2":"- Immunisation\n- Family planning\n- Hygiene\n- Keeping baby warm\n- Malaria Prevention","text3":"","instructions":"","instructions2":"","instructions3":"","instructions4":"","notes":"","refKey":"","images":{"contentTextImage":null,"image1":null,"image2":null,"image3":null}}</v>
+        <v/>
       </c>
     </row>
     <row r="65">
@@ -4772,22 +4772,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C65" t="str">
-        <v>Health Education/ Insecticide Net</v>
+        <v>Modifiable Factors</v>
       </c>
       <c r="D65" t="str">
-        <v>Health Ed/ ITN given</v>
+        <v>Modifiable</v>
       </c>
       <c r="E65" t="str">
         <v>form</v>
       </c>
       <c r="F65" t="str">
-        <v>HealthEd</v>
+        <v>ModFactor2</v>
       </c>
       <c r="G65" t="str">
-        <v>Has Health Education been given to mother?</v>
+        <v>Modifiable Factor 2</v>
       </c>
       <c r="H65" t="str">
-        <v>dropdown</v>
+        <v>string</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -4799,16 +4799,16 @@
         <v>No</v>
       </c>
       <c r="L65" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="M65" t="str">
         <v/>
       </c>
       <c r="N65" t="str">
-        <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"NO"}]</v>
+        <v/>
       </c>
       <c r="O65" t="str">
-        <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO'</v>
+        <v>$NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24' or $NeoTreeOutcome = 'BID'</v>
       </c>
       <c r="P65" t="str">
         <v/>
@@ -4840,22 +4840,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C66" t="str">
-        <v>Health Education/ Insecticide Net</v>
+        <v>Modifiable Factors</v>
       </c>
       <c r="D66" t="str">
-        <v>Health Ed/ ITN given</v>
+        <v>Modifiable</v>
       </c>
       <c r="E66" t="str">
         <v>form</v>
       </c>
       <c r="F66" t="str">
-        <v>ITN</v>
+        <v>ModFactor3</v>
       </c>
       <c r="G66" t="str">
-        <v>Has the mother been given an Insecticide Treated Net?</v>
+        <v>Modifiable Factor 3</v>
       </c>
       <c r="H66" t="str">
-        <v>dropdown</v>
+        <v>string</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -4867,16 +4867,16 @@
         <v>No</v>
       </c>
       <c r="L66" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="M66" t="str">
         <v/>
       </c>
       <c r="N66" t="str">
-        <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"}]</v>
+        <v/>
       </c>
       <c r="O66" t="str">
-        <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO'</v>
+        <v>$NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24' or $NeoTreeOutcome = 'BID'</v>
       </c>
       <c r="P66" t="str">
         <v/>
@@ -4908,22 +4908,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C67" t="str">
-        <v>Modifiable Factors</v>
+        <v>PATIENT INFORMATION</v>
       </c>
       <c r="D67" t="str">
-        <v>Modifiable</v>
+        <v>Sex</v>
       </c>
       <c r="E67" t="str">
-        <v>form</v>
+        <v>single_select</v>
       </c>
       <c r="F67" t="str">
-        <v>ModFactor1</v>
+        <v>Gender</v>
       </c>
       <c r="G67" t="str">
-        <v>Modifiable factor 1</v>
+        <v>Sex</v>
       </c>
       <c r="H67" t="str">
-        <v>string</v>
+        <v>single_select_option</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -4935,16 +4935,16 @@
         <v>No</v>
       </c>
       <c r="L67" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M67" t="str">
-        <v/>
+        <v>$NeoTreeOutcome = 'BID'</v>
       </c>
       <c r="N67" t="str">
-        <v/>
+        <v>[{"value":"M","valueLabel":"Male","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"F","valueLabel":"Female","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NS","valueLabel":"Not Sure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O67" t="str">
-        <v>$NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24' or $NeoTreeOutcome = 'BID'</v>
+        <v>$NeoTreeOutcome = 'BID'</v>
       </c>
       <c r="P67" t="str">
         <v/>
@@ -4976,22 +4976,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C68" t="str">
-        <v>Modifiable Factors</v>
+        <v>PATIENT INFORMATION</v>
       </c>
       <c r="D68" t="str">
-        <v>Modifiable</v>
+        <v xml:space="preserve">Age </v>
       </c>
       <c r="E68" t="str">
         <v>form</v>
       </c>
       <c r="F68" t="str">
-        <v>ModFactor2</v>
+        <v>BIDDOBYN</v>
       </c>
       <c r="G68" t="str">
-        <v>Modifiable Factor 2</v>
+        <v>Do you know the date/ time of birth</v>
       </c>
       <c r="H68" t="str">
-        <v>string</v>
+        <v>dropdown</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -5003,16 +5003,16 @@
         <v>No</v>
       </c>
       <c r="L68" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M68" t="str">
         <v/>
       </c>
       <c r="N68" t="str">
-        <v/>
+        <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O68" t="str">
-        <v>$NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24' or $NeoTreeOutcome = 'BID'</v>
+        <v>$NeoTreeOutcome = 'BID'</v>
       </c>
       <c r="P68" t="str">
         <v/>
@@ -5044,22 +5044,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C69" t="str">
-        <v>Modifiable Factors</v>
+        <v>PATIENT INFORMATION</v>
       </c>
       <c r="D69" t="str">
-        <v>Modifiable</v>
+        <v xml:space="preserve">Age </v>
       </c>
       <c r="E69" t="str">
         <v>form</v>
       </c>
       <c r="F69" t="str">
-        <v>ModFactor3</v>
+        <v>BIDDOBTOB</v>
       </c>
       <c r="G69" t="str">
-        <v>Modifiable Factor 3</v>
+        <v>Date and Time of Birth</v>
       </c>
       <c r="H69" t="str">
-        <v>string</v>
+        <v>datetime</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -5068,19 +5068,19 @@
         <v/>
       </c>
       <c r="K69" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="L69" t="str">
         <v>Yes</v>
       </c>
       <c r="M69" t="str">
-        <v/>
+        <v>$BIDDOBYN = 'Y'</v>
       </c>
       <c r="N69" t="str">
         <v/>
       </c>
       <c r="O69" t="str">
-        <v>$NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24' or $NeoTreeOutcome = 'BID'</v>
+        <v>$NeoTreeOutcome = 'BID'</v>
       </c>
       <c r="P69" t="str">
         <v/>
@@ -5115,19 +5115,19 @@
         <v>PATIENT INFORMATION</v>
       </c>
       <c r="D70" t="str">
-        <v>Sex</v>
+        <v xml:space="preserve">Age </v>
       </c>
       <c r="E70" t="str">
-        <v>single_select</v>
+        <v>form</v>
       </c>
       <c r="F70" t="str">
-        <v>Gender</v>
+        <v>BIDAgeB</v>
       </c>
       <c r="G70" t="str">
-        <v>Sex</v>
+        <v>Age (Days &amp; Hours)</v>
       </c>
       <c r="H70" t="str">
-        <v>single_select_option</v>
+        <v>period</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -5142,10 +5142,10 @@
         <v>No</v>
       </c>
       <c r="M70" t="str">
-        <v>$NeoTreeOutcome = 'BID'</v>
+        <v>$BIDDOBYN = 'Y'</v>
       </c>
       <c r="N70" t="str">
-        <v>[{"value":"M","valueLabel":"Male","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"F","valueLabel":"Female","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NS","valueLabel":"Not Sure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v/>
       </c>
       <c r="O70" t="str">
         <v>$NeoTreeOutcome = 'BID'</v>
@@ -5189,10 +5189,10 @@
         <v>form</v>
       </c>
       <c r="F71" t="str">
-        <v>BIDDOBYN</v>
+        <v>BIDAgeA</v>
       </c>
       <c r="G71" t="str">
-        <v>Do you know the date/ time of birth</v>
+        <v>Is the baby less than 1 week? (estimate)</v>
       </c>
       <c r="H71" t="str">
         <v>dropdown</v>
@@ -5210,10 +5210,10 @@
         <v>No</v>
       </c>
       <c r="M71" t="str">
-        <v/>
+        <v>$BIDDOBYN = 'N'</v>
       </c>
       <c r="N71" t="str">
-        <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
+        <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"}]</v>
       </c>
       <c r="O71" t="str">
         <v>$NeoTreeOutcome = 'BID'</v>
@@ -5257,13 +5257,13 @@
         <v>form</v>
       </c>
       <c r="F72" t="str">
-        <v>BIDDOBTOB</v>
+        <v>BIDAgeCat</v>
       </c>
       <c r="G72" t="str">
-        <v>Date and Time of Birth</v>
+        <v>Age Category? (estimate)</v>
       </c>
       <c r="H72" t="str">
-        <v>datetime</v>
+        <v>dropdown</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -5272,16 +5272,16 @@
         <v/>
       </c>
       <c r="K72" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="L72" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M72" t="str">
-        <v>$BIDDOBYN = 'Y'</v>
+        <v>$BIDAgeA = 'Y'</v>
       </c>
       <c r="N72" t="str">
-        <v/>
+        <v>[{"value":"FNB","valueLabel":"Fresh Newborn (&lt; 2 hours old)"},{"value":"NB24","valueLabel":"Newborn (2 - 23 hrs old)"},{"value":"NB48","valueLabel":"Newborn (1 day - 1 day 23 hrs old)"},{"value":"INF72","valueLabel":"Infant (2 days - 2 days 23 hrs old)"},{"value":"INF","valueLabel":"Infant (&gt; 3 days old)"}]</v>
       </c>
       <c r="O72" t="str">
         <v>$NeoTreeOutcome = 'BID'</v>
@@ -5325,13 +5325,13 @@
         <v>form</v>
       </c>
       <c r="F73" t="str">
-        <v>BIDAgeB</v>
+        <v>TypeBirth</v>
       </c>
       <c r="G73" t="str">
-        <v>Age (Days &amp; Hours)</v>
+        <v>Type of Birth</v>
       </c>
       <c r="H73" t="str">
-        <v>period</v>
+        <v>dropdown</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -5346,10 +5346,10 @@
         <v>No</v>
       </c>
       <c r="M73" t="str">
-        <v>$BIDDOBYN = 'Y'</v>
+        <v>$TypeBID != 'DU'</v>
       </c>
       <c r="N73" t="str">
-        <v/>
+        <v>[{"value":"S","valueLabel":"Single"},{"value":"Tw1","valueLabel":"1st Twin"},{"value":"Tw2","valueLabel":"2nd Twin"},{"value":"Tr1","valueLabel":"1st Triplet"},{"value":"Tr2","valueLabel":"2nd Triplet"},{"value":"Tr3","valueLabel":"3rd Triplet"},{"value":"Q1","valueLabel":"1st Quadruplet"},{"value":"Q2","valueLabel":"2nd Quadruplet"},{"value":"Q3","valueLabel":"3rd Quadruplet"},{"value":"Q4","valueLabel":"4th Quadruplet"}]</v>
       </c>
       <c r="O73" t="str">
         <v>$NeoTreeOutcome = 'BID'</v>
@@ -5387,19 +5387,19 @@
         <v>PATIENT INFORMATION</v>
       </c>
       <c r="D74" t="str">
-        <v xml:space="preserve">Age </v>
+        <v>Weight</v>
       </c>
       <c r="E74" t="str">
         <v>form</v>
       </c>
       <c r="F74" t="str">
-        <v>BIDAgeA</v>
+        <v>BirthWeight</v>
       </c>
       <c r="G74" t="str">
-        <v>Is the baby less than 1 week? (estimate)</v>
+        <v>Birth Weight (g)</v>
       </c>
       <c r="H74" t="str">
-        <v>dropdown</v>
+        <v>number</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -5411,13 +5411,13 @@
         <v>No</v>
       </c>
       <c r="L74" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="M74" t="str">
-        <v>$BIDDOBYN = 'N'</v>
+        <v>$TypeBID != 'DU'</v>
       </c>
       <c r="N74" t="str">
-        <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"}]</v>
+        <v/>
       </c>
       <c r="O74" t="str">
         <v>$NeoTreeOutcome = 'BID'</v>
@@ -5455,19 +5455,19 @@
         <v>PATIENT INFORMATION</v>
       </c>
       <c r="D75" t="str">
-        <v xml:space="preserve">Age </v>
+        <v>Weight</v>
       </c>
       <c r="E75" t="str">
         <v>form</v>
       </c>
       <c r="F75" t="str">
-        <v>BIDAgeCat</v>
+        <v>DischWeight</v>
       </c>
       <c r="G75" t="str">
-        <v>Age Category? (estimate)</v>
+        <v>Last recorded weight (g)</v>
       </c>
       <c r="H75" t="str">
-        <v>dropdown</v>
+        <v>number</v>
       </c>
       <c r="I75" t="str">
         <v/>
@@ -5482,10 +5482,10 @@
         <v>No</v>
       </c>
       <c r="M75" t="str">
-        <v>$BIDAgeA = 'Y'</v>
+        <v/>
       </c>
       <c r="N75" t="str">
-        <v>[{"value":"FNB","valueLabel":"Fresh Newborn (&lt; 2 hours old)"},{"value":"NB24","valueLabel":"Newborn (2 - 23 hrs old)"},{"value":"NB48","valueLabel":"Newborn (1 day - 1 day 23 hrs old)"},{"value":"INF72","valueLabel":"Infant (2 days - 2 days 23 hrs old)"},{"value":"INF","valueLabel":"Infant (&gt; 3 days old)"}]</v>
+        <v/>
       </c>
       <c r="O75" t="str">
         <v>$NeoTreeOutcome = 'BID'</v>
@@ -5523,19 +5523,19 @@
         <v>PATIENT INFORMATION</v>
       </c>
       <c r="D76" t="str">
-        <v xml:space="preserve">Age </v>
+        <v>Weight</v>
       </c>
       <c r="E76" t="str">
         <v>form</v>
       </c>
       <c r="F76" t="str">
-        <v>TypeBirth</v>
+        <v>DateDischWeight</v>
       </c>
       <c r="G76" t="str">
-        <v>Type of Birth</v>
+        <v>Date of last recorded weight</v>
       </c>
       <c r="H76" t="str">
-        <v>dropdown</v>
+        <v>datetime</v>
       </c>
       <c r="I76" t="str">
         <v/>
@@ -5550,10 +5550,10 @@
         <v>No</v>
       </c>
       <c r="M76" t="str">
-        <v>$TypeBID != 'DU'</v>
+        <v/>
       </c>
       <c r="N76" t="str">
-        <v>[{"value":"S","valueLabel":"Single"},{"value":"Tw1","valueLabel":"1st Twin"},{"value":"Tw2","valueLabel":"2nd Twin"},{"value":"Tr1","valueLabel":"1st Triplet"},{"value":"Tr2","valueLabel":"2nd Triplet"},{"value":"Tr3","valueLabel":"3rd Triplet"},{"value":"Q1","valueLabel":"1st Quadruplet"},{"value":"Q2","valueLabel":"2nd Quadruplet"},{"value":"Q3","valueLabel":"3rd Quadruplet"},{"value":"Q4","valueLabel":"4th Quadruplet"}]</v>
+        <v/>
       </c>
       <c r="O76" t="str">
         <v>$NeoTreeOutcome = 'BID'</v>
@@ -5591,16 +5591,16 @@
         <v>PATIENT INFORMATION</v>
       </c>
       <c r="D77" t="str">
-        <v>Weight</v>
+        <v>Gestation</v>
       </c>
       <c r="E77" t="str">
         <v>form</v>
       </c>
       <c r="F77" t="str">
-        <v>BirthWeight</v>
+        <v>Gestation</v>
       </c>
       <c r="G77" t="str">
-        <v>Birth weight (g)</v>
+        <v>Gestation (wks)</v>
       </c>
       <c r="H77" t="str">
         <v>number</v>
@@ -5615,16 +5615,16 @@
         <v>No</v>
       </c>
       <c r="L77" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M77" t="str">
-        <v>$TypeBID != 'DU'</v>
+        <v/>
       </c>
       <c r="N77" t="str">
         <v/>
       </c>
       <c r="O77" t="str">
-        <v>$NeoTreeOutcome = 'BID'</v>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="P77" t="str">
         <v/>
@@ -5659,19 +5659,19 @@
         <v>PATIENT INFORMATION</v>
       </c>
       <c r="D78" t="str">
-        <v>Weight</v>
+        <v>Gestation</v>
       </c>
       <c r="E78" t="str">
         <v>form</v>
       </c>
       <c r="F78" t="str">
-        <v>DischWeight</v>
+        <v>MethodEstGest</v>
       </c>
       <c r="G78" t="str">
-        <v>Last recorded weight (g)</v>
+        <v>Method of estimating gestation</v>
       </c>
       <c r="H78" t="str">
-        <v>number</v>
+        <v>dropdown</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -5689,10 +5689,10 @@
         <v/>
       </c>
       <c r="N78" t="str">
-        <v/>
+        <v>[{"value":"FundHt","valueLabel":"Fundal height"},{"value":"LMP","valueLabel":"Length of pregnancy / Last Mestrual Period (LMP)"},{"value":"USS","valueLabel":"USS"},{"value":"MatSc","valueLabel":"Maturity score"}]</v>
       </c>
       <c r="O78" t="str">
-        <v>$NeoTreeOutcome = 'BID'</v>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="P78" t="str">
         <v/>
@@ -5724,22 +5724,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C79" t="str">
-        <v>PATIENT INFORMATION</v>
+        <v>PLACE OF ORIGIN</v>
       </c>
       <c r="D79" t="str">
-        <v>Weight</v>
+        <v>From In or Out</v>
       </c>
       <c r="E79" t="str">
-        <v>form</v>
+        <v>yesno</v>
       </c>
       <c r="F79" t="str">
-        <v>DateDischWeight</v>
+        <v>InOrOut</v>
       </c>
       <c r="G79" t="str">
-        <v>Date of last recorded weight</v>
+        <v>Admitted from KCH?</v>
       </c>
       <c r="H79" t="str">
-        <v>datetime</v>
+        <v>boolean</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -5754,13 +5754,13 @@
         <v>No</v>
       </c>
       <c r="M79" t="str">
-        <v/>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="N79" t="str">
-        <v/>
+        <v>[{"value":"true","valueLabel":"Within this facility"},{"value":"false","valueLabel":"Outside this facility"}]</v>
       </c>
       <c r="O79" t="str">
-        <v>$NeoTreeOutcome = 'BID'</v>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="P79" t="str">
         <v/>
@@ -5792,22 +5792,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C80" t="str">
-        <v>PATIENT INFORMATION</v>
+        <v>PLACE OF ORIGIN</v>
       </c>
       <c r="D80" t="str">
-        <v>Gestation</v>
+        <v xml:space="preserve">In: Admitted from </v>
       </c>
       <c r="E80" t="str">
-        <v>form</v>
+        <v>single_select</v>
       </c>
       <c r="F80" t="str">
-        <v>Gestation</v>
+        <v>AdmittedFrom</v>
       </c>
       <c r="G80" t="str">
-        <v>Gestation (wks)</v>
+        <v>Admitted from</v>
       </c>
       <c r="H80" t="str">
-        <v>number</v>
+        <v>single_select_option</v>
       </c>
       <c r="I80" t="str">
         <v/>
@@ -5822,13 +5822,13 @@
         <v>No</v>
       </c>
       <c r="M80" t="str">
-        <v/>
+        <v>$InOrOut = true and $TypeBID != 'DU'</v>
       </c>
       <c r="N80" t="str">
-        <v/>
+        <v>[{"value":"LW","valueLabel":"Labour ward (LW)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PNW","valueLabel":"Post Natal Ward (PNW)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TH","valueLabel":"Theatre","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"KMC","valueLabel":"Kangaroo Mother Care (KMC)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ANC","valueLabel":"Antenatal ward","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PW","valueLabel":"Paying ward","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O80" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v>$InOrOut = true and $TypeBID != 'DU'</v>
       </c>
       <c r="P80" t="str">
         <v/>
@@ -5860,22 +5860,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C81" t="str">
-        <v>PATIENT INFORMATION</v>
+        <v>PLACE OF ORIGIN</v>
       </c>
       <c r="D81" t="str">
-        <v>Gestation</v>
+        <v>Out: home/facility</v>
       </c>
       <c r="E81" t="str">
-        <v>form</v>
+        <v>single_select</v>
       </c>
       <c r="F81" t="str">
-        <v>MethodEstGest</v>
+        <v>ReferredFrom2</v>
       </c>
       <c r="G81" t="str">
-        <v>Method of estimating gestation</v>
+        <v>Referred from</v>
       </c>
       <c r="H81" t="str">
-        <v>dropdown</v>
+        <v>single_select_option</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -5890,13 +5890,13 @@
         <v>No</v>
       </c>
       <c r="M81" t="str">
-        <v/>
+        <v>$InOrOut = false</v>
       </c>
       <c r="N81" t="str">
-        <v>[{"value":"FundHt","valueLabel":"Fundal height"},{"value":"LMP","valueLabel":"Length of pregnancy / Last Mestrual Period (LMP)"},{"value":"USS","valueLabel":"USS"},{"value":"MatSc","valueLabel":"Maturity score"}]</v>
+        <v>[{"value":"H","valueLabel":"Home - Self Referral","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"F","valueLabel":"Other facility","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O81" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v>$InOrOut = false</v>
       </c>
       <c r="P81" t="str">
         <v/>
@@ -5931,19 +5931,19 @@
         <v>PLACE OF ORIGIN</v>
       </c>
       <c r="D82" t="str">
-        <v>From In or Out</v>
+        <v>Out: Referred from</v>
       </c>
       <c r="E82" t="str">
-        <v>yesno</v>
+        <v>single_select</v>
       </c>
       <c r="F82" t="str">
-        <v>InOrOut</v>
+        <v>ReferredFrom</v>
       </c>
       <c r="G82" t="str">
-        <v>Admitted from KCH?</v>
+        <v>Name of referring facility</v>
       </c>
       <c r="H82" t="str">
-        <v>boolean</v>
+        <v>single_select_option</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -5958,13 +5958,13 @@
         <v>No</v>
       </c>
       <c r="M82" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v>$ReferredFrom2 = 'F'</v>
       </c>
       <c r="N82" t="str">
-        <v>[{"value":"true","valueLabel":"Within this facility"},{"value":"false","valueLabel":"Outside this facility"}]</v>
+        <v>[{"value":"A25","valueLabel":"Area 25 HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Lumb","valueLabel":"Lumbadzi HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Bwai","valueLabel":"Bwaila Hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Kab","valueLabel":"Kabudula rural hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mit","valueLabel":"Mitundu community hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mchi","valueLabel":"Mchinji District Hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Sal","valueLabel":"Salima district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Dowa","valueLabel":"Dowa district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CLI","valueLabel":"Child Legacy International","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Kaw","valueLabel":"Kawale HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"A18","valueLabel":"Area 18 HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Dedza","valueLabel":"Dedza district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Kas","valueLabel":"Kasungu district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Nkhot","valueLabel":"Nkhotakota district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mzuzu","valueLabel":"Mzuzu central hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O82" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v>$ReferredFrom2 = 'F'</v>
       </c>
       <c r="P82" t="str">
         <v/>
@@ -5996,22 +5996,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C83" t="str">
-        <v>PLACE OF ORIGIN</v>
+        <v>PlACE OF ORIGIN</v>
       </c>
       <c r="D83" t="str">
-        <v xml:space="preserve">In: Admitted from </v>
+        <v>OtherReferralFacility</v>
       </c>
       <c r="E83" t="str">
-        <v>single_select</v>
+        <v>form</v>
       </c>
       <c r="F83" t="str">
-        <v>AdmittedFrom</v>
+        <v>OtherReferralFacility</v>
       </c>
       <c r="G83" t="str">
-        <v>Admitted from</v>
+        <v>Name of Facility</v>
       </c>
       <c r="H83" t="str">
-        <v>single_select_option</v>
+        <v>string</v>
       </c>
       <c r="I83" t="str">
         <v/>
@@ -6026,13 +6026,13 @@
         <v>No</v>
       </c>
       <c r="M83" t="str">
-        <v>$InOrOut = true and $TypeBID != 'DU'</v>
+        <v/>
       </c>
       <c r="N83" t="str">
-        <v>[{"value":"LW","valueLabel":"Labour ward (LW)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PNW","valueLabel":"Post Natal Ward (PNW)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TH","valueLabel":"Theatre","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"KMC","valueLabel":"Kangaroo Mother Care (KMC)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ANC","valueLabel":"Antenatal ward","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PW","valueLabel":"Paying ward","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v/>
       </c>
       <c r="O83" t="str">
-        <v>$InOrOut = true and $TypeBID != 'DU'</v>
+        <v>$ReferredFrom = 'O'</v>
       </c>
       <c r="P83" t="str">
         <v/>
@@ -6067,19 +6067,19 @@
         <v>PLACE OF ORIGIN</v>
       </c>
       <c r="D84" t="str">
-        <v>Out: home/facility</v>
+        <v>Birth Place Same</v>
       </c>
       <c r="E84" t="str">
-        <v>single_select</v>
+        <v>yesno</v>
       </c>
       <c r="F84" t="str">
-        <v>ReferredFrom2</v>
+        <v>BirthPlaceSame</v>
       </c>
       <c r="G84" t="str">
-        <v>Referred from</v>
+        <v>Birth place same?</v>
       </c>
       <c r="H84" t="str">
-        <v>single_select_option</v>
+        <v>boolean</v>
       </c>
       <c r="I84" t="str">
         <v/>
@@ -6091,16 +6091,16 @@
         <v>No</v>
       </c>
       <c r="L84" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="M84" t="str">
-        <v>$InOrOut = false</v>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="N84" t="str">
-        <v>[{"value":"H","valueLabel":"Home - Self Referral","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"F","valueLabel":"Other facility","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"true","valueLabel":"Yes"},{"value":"false","valueLabel":"No"}]</v>
       </c>
       <c r="O84" t="str">
-        <v>$InOrOut = false</v>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="P84" t="str">
         <v/>
@@ -6135,16 +6135,16 @@
         <v>PLACE OF ORIGIN</v>
       </c>
       <c r="D85" t="str">
-        <v>Out: Referred from</v>
+        <v>Birth Place</v>
       </c>
       <c r="E85" t="str">
         <v>single_select</v>
       </c>
       <c r="F85" t="str">
-        <v>ReferredFrom</v>
+        <v>PlaceBirth</v>
       </c>
       <c r="G85" t="str">
-        <v>Name of referring facility</v>
+        <v>Place of birth</v>
       </c>
       <c r="H85" t="str">
         <v>single_select_option</v>
@@ -6162,13 +6162,13 @@
         <v>No</v>
       </c>
       <c r="M85" t="str">
-        <v>$ReferredFrom2 = 'F'</v>
+        <v>$BirthPlaceSame = false</v>
       </c>
       <c r="N85" t="str">
-        <v>[{"value":"A25","valueLabel":"Area 25 HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Lumb","valueLabel":"Lumbadzi HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Bwai","valueLabel":"Bwaila Hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Kab","valueLabel":"Kabudula rural hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mit","valueLabel":"Mitundu community hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mchi","valueLabel":"Mchinji District Hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Sal","valueLabel":"Salima district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Dowa","valueLabel":"Dowa district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CLI","valueLabel":"Child Legacy International","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Kaw","valueLabel":"Kawale HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"A18","valueLabel":"Area 18 HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Dedza","valueLabel":"Dedza district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Kas","valueLabel":"Kasungu district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Nkhot","valueLabel":"Nkhotakota district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mzuzu","valueLabel":"Mzuzu central hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"Hosp","valueLabel":"Hospital ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HC","valueLabel":"Health Centre","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born on the way to hospital (in transit)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Home","valueLabel":"Home","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O85" t="str">
-        <v>$ReferredFrom2 = 'F'</v>
+        <v>$BirthPlaceSame = false</v>
       </c>
       <c r="P85" t="str">
         <v/>
@@ -6200,22 +6200,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C86" t="str">
-        <v>PlACE OF ORIGIN</v>
+        <v>PLACE OF ORIGIN</v>
       </c>
       <c r="D86" t="str">
-        <v>OtherReferralFacility</v>
+        <v>Name Facility</v>
       </c>
       <c r="E86" t="str">
-        <v>form</v>
+        <v>single_select</v>
       </c>
       <c r="F86" t="str">
-        <v>OtherReferralFacility</v>
+        <v>BirthFacility</v>
       </c>
       <c r="G86" t="str">
-        <v xml:space="preserve">Name of Facility </v>
+        <v>Name of Facility</v>
       </c>
       <c r="H86" t="str">
-        <v>string</v>
+        <v>single_select_option</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -6230,13 +6230,13 @@
         <v>No</v>
       </c>
       <c r="M86" t="str">
-        <v/>
+        <v>$PlaceBirth = 'Hosp' or $PlaceBirth = 'HC'</v>
       </c>
       <c r="N86" t="str">
-        <v/>
+        <v>[{"value":"A25","valueLabel":"Area 25 HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Lum","valueLabel":"Lumbadzi HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Bwai","valueLabel":"Bwaila Hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Kab","valueLabel":"Kabudula rural hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mit","valueLabel":"Mitundu community hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mchi","valueLabel":"Mchinji District Hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Sal","valueLabel":"Salima district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Dowa","valueLabel":"Dowa district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CLI","valueLabel":"Child Legacy International Hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Kaw","valueLabel":"Kawale HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"A18","valueLabel":"Area 18 HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ded","valueLabel":"Dedza district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Kas","valueLabel":"Kasungu district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Nkhot","valueLabel":"Nkhotakota district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mzuzu","valueLabel":"Mzuzu central hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O86" t="str">
-        <v>$ReferredFrom = 'O'</v>
+        <v>$PlaceBirth = 'Hosp' or $PlaceBirth = 'HC'</v>
       </c>
       <c r="P86" t="str">
         <v/>
@@ -6271,19 +6271,19 @@
         <v>PLACE OF ORIGIN</v>
       </c>
       <c r="D87" t="str">
-        <v>Birth Place Same</v>
+        <v>OtherBirthFacility</v>
       </c>
       <c r="E87" t="str">
-        <v>yesno</v>
+        <v>form</v>
       </c>
       <c r="F87" t="str">
-        <v>BirthPlaceSame</v>
+        <v>OtherBirthFacility</v>
       </c>
       <c r="G87" t="str">
-        <v>Birth place same?</v>
+        <v>Name of facility:</v>
       </c>
       <c r="H87" t="str">
-        <v>boolean</v>
+        <v>string</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -6295,16 +6295,16 @@
         <v>No</v>
       </c>
       <c r="L87" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M87" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v/>
       </c>
       <c r="N87" t="str">
-        <v>[{"value":"true","valueLabel":"Yes"},{"value":"false","valueLabel":"No"}]</v>
+        <v/>
       </c>
       <c r="O87" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v>$BirthFacility = 'O'</v>
       </c>
       <c r="P87" t="str">
         <v/>
@@ -6336,22 +6336,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C88" t="str">
-        <v>PLACE OF ORIGIN</v>
+        <v>MATERNAL DETAILS</v>
       </c>
       <c r="D88" t="str">
-        <v>Birth Place</v>
+        <v>Maternal Address</v>
       </c>
       <c r="E88" t="str">
-        <v>single_select</v>
+        <v>form</v>
       </c>
       <c r="F88" t="str">
-        <v>PlaceBirth</v>
+        <v>MotherAddressVillage</v>
       </c>
       <c r="G88" t="str">
-        <v>Place of birth</v>
+        <v>Mother's Village</v>
       </c>
       <c r="H88" t="str">
-        <v>single_select_option</v>
+        <v>string</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -6360,19 +6360,19 @@
         <v/>
       </c>
       <c r="K88" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="L88" t="str">
         <v>No</v>
       </c>
       <c r="M88" t="str">
-        <v>$BirthPlaceSame = false</v>
+        <v/>
       </c>
       <c r="N88" t="str">
-        <v>[{"value":"Hosp","valueLabel":"Hospital ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HC","valueLabel":"Health Centre","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born on the way to hospital (in transit)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Home","valueLabel":"Home","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v/>
       </c>
       <c r="O88" t="str">
-        <v>$BirthPlaceSame = false</v>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="P88" t="str">
         <v/>
@@ -6404,22 +6404,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C89" t="str">
-        <v>PLACE OF ORIGIN</v>
+        <v>MATERNAL DETAILS</v>
       </c>
       <c r="D89" t="str">
-        <v>Name Facility</v>
+        <v>Maternal Address</v>
       </c>
       <c r="E89" t="str">
-        <v>single_select</v>
+        <v>form</v>
       </c>
       <c r="F89" t="str">
-        <v>BirthFacility</v>
+        <v>MatPhysAddressDistrict</v>
       </c>
       <c r="G89" t="str">
-        <v>Name of Facility</v>
+        <v>Mother's District</v>
       </c>
       <c r="H89" t="str">
-        <v>single_select_option</v>
+        <v>dropdown</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -6434,13 +6434,13 @@
         <v>No</v>
       </c>
       <c r="M89" t="str">
-        <v>$PlaceBirth = 'Hosp' or $PlaceBirth = 'HC'</v>
+        <v/>
       </c>
       <c r="N89" t="str">
-        <v>[{"value":"A25","valueLabel":"Area 25 HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Lum","valueLabel":"Lumbadzi HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Bwai","valueLabel":"Bwaila Hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Kab","valueLabel":"Kabudula rural hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mit","valueLabel":"Mitundu community hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mchi","valueLabel":"Mchinji District Hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Sal","valueLabel":"Salima district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Dowa","valueLabel":"Dowa district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CLI","valueLabel":"Child Legacy International Hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Kaw","valueLabel":"Kawale HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"A18","valueLabel":"Area 18 HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ded","valueLabel":"Dedza district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Kas","valueLabel":"Kasungu district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Nkhot","valueLabel":"Nkhotakota district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mzuzu","valueLabel":"Mzuzu central hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"LL","valueLabel":"Lilongwe"},{"value":"B","valueLabel":"Balaka"},{"value":"BL","valueLabel":"Blantyre"},{"value":"BLC","valueLabel":"Blantyre City"},{"value":"CHK","valueLabel":"Chikwawa"},{"value":"CHR","valueLabel":"Chiradzulu"},{"value":"CHP","valueLabel":"Chitipa"},{"value":"DE","valueLabel":"Dedza"},{"value":"DO","valueLabel":"Dowa"},{"value":"KR","valueLabel":"Karonga"},{"value":"KS","valueLabel":"Kasungu"},{"value":"LK","valueLabel":"Likoma"},{"value":"MC","valueLabel":"Machinga"},{"value":"MG","valueLabel":"Mangochi"},{"value":"MCH","valueLabel":"Mchinji"},{"value":"MU","valueLabel":"Mulanje"},{"value":"MW","valueLabel":"Mwanza"},{"value":"MB","valueLabel":"Mzimba"},{"value":"MZ","valueLabel":"Mzuzu City"},{"value":"NE","valueLabel":"Neno"},{"value":"NKB","valueLabel":"Nkata bay"},{"value":"NKK","valueLabel":"Nkhotakota"},{"value":"NS","valueLabel":"Nsanje"},{"value":"NCU","valueLabel":"Ntcheu"},{"value":"NCI","valueLabel":"Ntchisi"},{"value":"PH","valueLabel":"Phalombe"},{"value":"RU","valueLabel":"Rumphi"},{"value":"SA","valueLabel":"Salima"},{"value":"TH","valueLabel":"Thyolo"},{"value":"Z","valueLabel":"Zomba"}]</v>
       </c>
       <c r="O89" t="str">
-        <v>$PlaceBirth = 'Hosp' or $PlaceBirth = 'HC'</v>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="P89" t="str">
         <v/>
@@ -6472,22 +6472,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C90" t="str">
-        <v>PLACE OF ORIGIN</v>
+        <v>MATERNAL DETAILS</v>
       </c>
       <c r="D90" t="str">
-        <v>OtherBirthFacility</v>
+        <v>Maternal Age</v>
       </c>
       <c r="E90" t="str">
         <v>form</v>
       </c>
       <c r="F90" t="str">
-        <v>OtherBirthFacility</v>
+        <v>MatAgeYrs</v>
       </c>
       <c r="G90" t="str">
-        <v xml:space="preserve">Name of facility: </v>
+        <v>Age of Mother (yrs)</v>
       </c>
       <c r="H90" t="str">
-        <v>string</v>
+        <v>number</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -6508,7 +6508,7 @@
         <v/>
       </c>
       <c r="O90" t="str">
-        <v>$BirthFacility = 'O'</v>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="P90" t="str">
         <v/>
@@ -6543,19 +6543,19 @@
         <v>MATERNAL DETAILS</v>
       </c>
       <c r="D91" t="str">
-        <v>Maternal Address</v>
+        <v xml:space="preserve">Marital Status </v>
       </c>
       <c r="E91" t="str">
-        <v>form</v>
+        <v>single_select</v>
       </c>
       <c r="F91" t="str">
-        <v>MotherAddressVillage</v>
+        <v>MaritalStat</v>
       </c>
       <c r="G91" t="str">
-        <v>Mother's Village</v>
+        <v>Marital status</v>
       </c>
       <c r="H91" t="str">
-        <v>string</v>
+        <v>single_select_option</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -6564,16 +6564,16 @@
         <v/>
       </c>
       <c r="K91" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="L91" t="str">
         <v>No</v>
       </c>
       <c r="M91" t="str">
-        <v/>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="N91" t="str">
-        <v/>
+        <v>[{"value":"MAR","valueLabel":"Married","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DIV","valueLabel":"Divorced","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"WID","valueLabel":"Widowed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"S","valueLabel":"Single","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O91" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -6611,19 +6611,19 @@
         <v>MATERNAL DETAILS</v>
       </c>
       <c r="D92" t="str">
-        <v>Maternal Address</v>
+        <v>Maternal Ethnicity</v>
       </c>
       <c r="E92" t="str">
-        <v>form</v>
+        <v>single_select</v>
       </c>
       <c r="F92" t="str">
-        <v>MatPhysAddressDistrict</v>
+        <v>Ethnicity</v>
       </c>
       <c r="G92" t="str">
-        <v>Mother's District</v>
+        <v>Ethnicity</v>
       </c>
       <c r="H92" t="str">
-        <v>dropdown</v>
+        <v>single_select_option</v>
       </c>
       <c r="I92" t="str">
         <v/>
@@ -6638,10 +6638,10 @@
         <v>No</v>
       </c>
       <c r="M92" t="str">
-        <v/>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="N92" t="str">
-        <v>[{"value":"LL","valueLabel":"Lilongwe"},{"value":"B","valueLabel":"Balaka"},{"value":"BL","valueLabel":"Blantyre"},{"value":"BLC","valueLabel":"Blantyre City"},{"value":"CHK","valueLabel":"Chikwawa"},{"value":"CHR","valueLabel":"Chiradzulu"},{"value":"CHP","valueLabel":"Chitipa"},{"value":"DE","valueLabel":"Dedza"},{"value":"DO","valueLabel":"Dowa"},{"value":"KR","valueLabel":"Karonga"},{"value":"KS","valueLabel":"Kasungu"},{"value":"LK","valueLabel":"Likoma"},{"value":"MC","valueLabel":"Machinga"},{"value":"MG","valueLabel":"Mangochi"},{"value":"MCH","valueLabel":"Mchinji"},{"value":"MU","valueLabel":"Mulanje"},{"value":"MW","valueLabel":"Mwanza"},{"value":"MB","valueLabel":"Mzimba"},{"value":"MZ","valueLabel":"Mzuzu City"},{"value":"NE","valueLabel":"Neno"},{"value":"NKB","valueLabel":"Nkata bay"},{"value":"NKK","valueLabel":"Nkhotakota"},{"value":"NS","valueLabel":"Nsanje"},{"value":"NCU","valueLabel":"Ntcheu"},{"value":"NCI","valueLabel":"Ntchisi"},{"value":"PH","valueLabel":"Phalombe"},{"value":"RU","valueLabel":"Rumphi"},{"value":"SA","valueLabel":"Salima"},{"value":"TH","valueLabel":"Thyolo"},{"value":"Z","valueLabel":"Zomba"}]</v>
+        <v>[{"value":"M","valueLabel":"Malawian","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MO","valueLabel":"Mozambican","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"B","valueLabel":"Botswana","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BU","valueLabel":"Burundian","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CA","valueLabel":"Central African","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ET","valueLabel":"Ethiopian","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ER","valueLabel":"Eritrean","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"K","valueLabel":"Kenyan","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"R","valueLabel":"Rwandan","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SL","valueLabel":"Sierra Leonean","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"S","valueLabel":"Somali","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SA","valueLabel":"South African","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"T","valueLabel":"Tanzanian","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"U","valueLabel":"Ugandan","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ZAM","valueLabel":"Zambian","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ZIM","valueLabel":"Zimbabwe","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O92" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -6679,19 +6679,19 @@
         <v>MATERNAL DETAILS</v>
       </c>
       <c r="D93" t="str">
-        <v>Maternal Age</v>
+        <v>Maternal Ethnicity Other</v>
       </c>
       <c r="E93" t="str">
         <v>form</v>
       </c>
       <c r="F93" t="str">
-        <v>MatAgeYrs</v>
+        <v>EthnicityOther</v>
       </c>
       <c r="G93" t="str">
-        <v>Age of Mother (yrs)</v>
+        <v>If other, what is your ethnicity?</v>
       </c>
       <c r="H93" t="str">
-        <v>number</v>
+        <v>string</v>
       </c>
       <c r="I93" t="str">
         <v/>
@@ -6712,7 +6712,7 @@
         <v/>
       </c>
       <c r="O93" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v>$NeoTreeOutcome = 'BID' and $Ethnicity = 'O'</v>
       </c>
       <c r="P93" t="str">
         <v/>
@@ -6747,16 +6747,16 @@
         <v>MATERNAL DETAILS</v>
       </c>
       <c r="D94" t="str">
-        <v xml:space="preserve">Marital Status </v>
+        <v>Maternal Tribe</v>
       </c>
       <c r="E94" t="str">
         <v>single_select</v>
       </c>
       <c r="F94" t="str">
-        <v>MaritalStat</v>
+        <v>Tribe</v>
       </c>
       <c r="G94" t="str">
-        <v>Marital status</v>
+        <v>Mother's Tribe</v>
       </c>
       <c r="H94" t="str">
         <v>single_select_option</v>
@@ -6777,7 +6777,7 @@
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="N94" t="str">
-        <v>[{"value":"MAR","valueLabel":"Married","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DIV","valueLabel":"Divorced","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"WID","valueLabel":"Widowed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"S","valueLabel":"Single","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"Ch","valueLabel":"Chewa","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CH","valueLabel":"Chinyanja","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Lo","valueLabel":"Lomwe","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M","valueLabel":"Mang'anja","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ng","valueLabel":"Ngoni","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NY","valueLabel":"Nyanja","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"S","valueLabel":"Sena","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Tu","valueLabel":"Tumbuka","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"To","valueLabel":"Tonga","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ya","valueLabel":"Yao (Mchawa)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"None","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O94" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -6815,19 +6815,19 @@
         <v>MATERNAL DETAILS</v>
       </c>
       <c r="D95" t="str">
-        <v>Maternal Ethnicity</v>
+        <v xml:space="preserve">Maternal Tribe Other </v>
       </c>
       <c r="E95" t="str">
-        <v>single_select</v>
+        <v>form</v>
       </c>
       <c r="F95" t="str">
-        <v>Ethnicity</v>
+        <v>TribeOther</v>
       </c>
       <c r="G95" t="str">
-        <v>Ethnicity</v>
+        <v>If other, which tribe?</v>
       </c>
       <c r="H95" t="str">
-        <v>single_select_option</v>
+        <v>string</v>
       </c>
       <c r="I95" t="str">
         <v/>
@@ -6842,13 +6842,13 @@
         <v>No</v>
       </c>
       <c r="M95" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v/>
       </c>
       <c r="N95" t="str">
-        <v>[{"value":"M","valueLabel":"Malawian","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MO","valueLabel":"Mozambican","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"B","valueLabel":"Botswana","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BU","valueLabel":"Burundian","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CA","valueLabel":"Central African","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ET","valueLabel":"Ethiopian","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ER","valueLabel":"Eritrean","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"K","valueLabel":"Kenyan","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"R","valueLabel":"Rwandan","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SL","valueLabel":"Sierra Leonean","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"S","valueLabel":"Somali","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SA","valueLabel":"South African","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"T","valueLabel":"Tanzanian","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"U","valueLabel":"Ugandan","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ZAM","valueLabel":"Zambian","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ZIM","valueLabel":"Zimbabwe","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v/>
       </c>
       <c r="O95" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v>$NeoTreeOutcome = 'BID' and $Tribe = 'O'</v>
       </c>
       <c r="P95" t="str">
         <v/>
@@ -6883,19 +6883,19 @@
         <v>MATERNAL DETAILS</v>
       </c>
       <c r="D96" t="str">
-        <v>Maternal Ethnicity Other</v>
+        <v>Maternal Religion</v>
       </c>
       <c r="E96" t="str">
-        <v>form</v>
+        <v>single_select</v>
       </c>
       <c r="F96" t="str">
-        <v>EthnicityOther</v>
+        <v>Religion</v>
       </c>
       <c r="G96" t="str">
-        <v xml:space="preserve">If other, what is your ethnicity? </v>
+        <v>Mother's religion</v>
       </c>
       <c r="H96" t="str">
-        <v>string</v>
+        <v>single_select_option</v>
       </c>
       <c r="I96" t="str">
         <v/>
@@ -6910,13 +6910,13 @@
         <v>No</v>
       </c>
       <c r="M96" t="str">
-        <v/>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="N96" t="str">
-        <v/>
+        <v>[{"value":"A","valueLabel":"Anglican (Christian protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AOG","valueLabel":"Assemblies of god","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ba","valueLabel":"Baptist (Christian Protestant) ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CCAP","valueLabel":"Church of Central Africa (CCAP)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CFC","valueLabel":"Calvary Family Church ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"COC","valueLabel":"Church of Christ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CP","valueLabel":"Other Christian Protestant","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BB","valueLabel":"Bible Believers ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RC","valueLabel":"Roman Catholic (Christian) ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ECC","valueLabel":"Enlightened Christian Catholic (ECC)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MU","valueLabel":"Muslim","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"P","valueLabel":"Prespyterian","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SDA","valueLabel":"Seventh Day Adventist (SDA)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"JW","valueLabel":"Jehover's Witness","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LW","valueLabel":"Living Waters","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Z","valueLabel":"Zion","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AG","valueLabel":"Agnostic","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ATH","valueLabel":"Atheist","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O96" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $Ethnicity = 'O'</v>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="P96" t="str">
         <v/>
@@ -6951,19 +6951,19 @@
         <v>MATERNAL DETAILS</v>
       </c>
       <c r="D97" t="str">
-        <v>Maternal Tribe</v>
+        <v>Maternal Religion Other</v>
       </c>
       <c r="E97" t="str">
-        <v>single_select</v>
+        <v>form</v>
       </c>
       <c r="F97" t="str">
-        <v>Tribe</v>
+        <v>ReligionOther</v>
       </c>
       <c r="G97" t="str">
-        <v>Mother's Tribe</v>
+        <v>If other, which religion?</v>
       </c>
       <c r="H97" t="str">
-        <v>single_select_option</v>
+        <v>string</v>
       </c>
       <c r="I97" t="str">
         <v/>
@@ -6978,13 +6978,13 @@
         <v>No</v>
       </c>
       <c r="M97" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v/>
       </c>
       <c r="N97" t="str">
-        <v>[{"value":"Ch","valueLabel":"Chewa","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CH","valueLabel":"Chinyanja","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Lo","valueLabel":"Lomwe","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M","valueLabel":"Mang'anja","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ng","valueLabel":"Ngoni","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NY","valueLabel":"Nyanja","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"S","valueLabel":"Sena","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Tu","valueLabel":"Tumbuka","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"To","valueLabel":"Tonga","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ya","valueLabel":"Yao (Mchawa)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"None","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v/>
       </c>
       <c r="O97" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v>$NeoTreeOutcome = 'BID' and $Religion = 'O'</v>
       </c>
       <c r="P97" t="str">
         <v/>
@@ -7016,22 +7016,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C98" t="str">
-        <v>MATERNAL DETAILS</v>
+        <v>MATERNAL SEROSTATUS</v>
       </c>
       <c r="D98" t="str">
-        <v xml:space="preserve">Maternal Tribe Other </v>
+        <v>HIVtest</v>
       </c>
       <c r="E98" t="str">
-        <v>form</v>
+        <v>yesno</v>
       </c>
       <c r="F98" t="str">
-        <v>TribeOther</v>
+        <v>MatHIVtest</v>
       </c>
       <c r="G98" t="str">
-        <v xml:space="preserve">If other, which tribe? </v>
+        <v>Mother had HIV test?</v>
       </c>
       <c r="H98" t="str">
-        <v>string</v>
+        <v>boolean</v>
       </c>
       <c r="I98" t="str">
         <v/>
@@ -7046,13 +7046,13 @@
         <v>No</v>
       </c>
       <c r="M98" t="str">
-        <v/>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="N98" t="str">
-        <v/>
+        <v>[{"value":"true","valueLabel":"Yes"},{"value":"false","valueLabel":"No"}]</v>
       </c>
       <c r="O98" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $Tribe = 'O'</v>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="P98" t="str">
         <v/>
@@ -7084,22 +7084,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C99" t="str">
-        <v>MATERNAL DETAILS</v>
+        <v>MATERNAL SEROSTATUS</v>
       </c>
       <c r="D99" t="str">
-        <v>Maternal Religion</v>
+        <v xml:space="preserve">HIV TEST details </v>
       </c>
       <c r="E99" t="str">
-        <v>single_select</v>
+        <v>form</v>
       </c>
       <c r="F99" t="str">
-        <v>Religion</v>
+        <v>DateHIVtest</v>
       </c>
       <c r="G99" t="str">
-        <v>Mother's religion</v>
+        <v>When was this test?</v>
       </c>
       <c r="H99" t="str">
-        <v>single_select_option</v>
+        <v>date</v>
       </c>
       <c r="I99" t="str">
         <v/>
@@ -7111,16 +7111,16 @@
         <v>No</v>
       </c>
       <c r="L99" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="M99" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v/>
       </c>
       <c r="N99" t="str">
-        <v>[{"value":"A","valueLabel":"Anglican (Christian protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AOG","valueLabel":"Assemblies of god","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ba","valueLabel":"Baptist (Christian Protestant) ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CCAP","valueLabel":"Church of Central Africa (CCAP)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CFC","valueLabel":"Calvary Family Church ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"COC","valueLabel":"Church of Christ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CP","valueLabel":"Other Christian Protestant","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BB","valueLabel":"Bible Believers ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RC","valueLabel":"Roman Catholic (Christian) ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ECC","valueLabel":"Enlightened Christian Catholic (ECC)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MU","valueLabel":"Muslim","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"P","valueLabel":"Prespyterian","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SDA","valueLabel":"Seventh Day Adventist (SDA)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"JW","valueLabel":"Jehover's Witness","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LW","valueLabel":"Living Waters","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Z","valueLabel":"Zion","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AG","valueLabel":"Agnostic","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ATH","valueLabel":"Atheist","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v/>
       </c>
       <c r="O99" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v>$NeoTreeOutcome = 'BID' and $MatHIVtest = true</v>
       </c>
       <c r="P99" t="str">
         <v/>
@@ -7152,22 +7152,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C100" t="str">
-        <v>MATERNAL DETAILS</v>
+        <v>MATERNAL SEROSTATUS</v>
       </c>
       <c r="D100" t="str">
-        <v>Maternal Religion Other</v>
+        <v xml:space="preserve">HIV TEST details </v>
       </c>
       <c r="E100" t="str">
         <v>form</v>
       </c>
       <c r="F100" t="str">
-        <v>ReligionOther</v>
+        <v>TestThisPreg</v>
       </c>
       <c r="G100" t="str">
-        <v>If other, which religion?</v>
+        <v>Was the test during this pregnancy?</v>
       </c>
       <c r="H100" t="str">
-        <v>string</v>
+        <v>dropdown</v>
       </c>
       <c r="I100" t="str">
         <v/>
@@ -7185,10 +7185,10 @@
         <v/>
       </c>
       <c r="N100" t="str">
-        <v/>
+        <v>[{"value":"Y","valueLabel":"During this pregnancy"},{"value":"N","valueLabel":"Before this pregnancy"}]</v>
       </c>
       <c r="O100" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $Religion = 'O'</v>
+        <v>$NeoTreeOutcome = 'BID' and $MatHIVtest = true</v>
       </c>
       <c r="P100" t="str">
         <v/>
@@ -7223,19 +7223,19 @@
         <v>MATERNAL SEROSTATUS</v>
       </c>
       <c r="D101" t="str">
-        <v>HIVtest</v>
+        <v xml:space="preserve">HIV TEST details </v>
       </c>
       <c r="E101" t="str">
-        <v>yesno</v>
+        <v>form</v>
       </c>
       <c r="F101" t="str">
-        <v>MatHIVtest</v>
+        <v>HIVtestResult</v>
       </c>
       <c r="G101" t="str">
-        <v>Mother had HIV test?</v>
+        <v>What was the Result?</v>
       </c>
       <c r="H101" t="str">
-        <v>boolean</v>
+        <v>dropdown</v>
       </c>
       <c r="I101" t="str">
         <v/>
@@ -7250,13 +7250,13 @@
         <v>No</v>
       </c>
       <c r="M101" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v/>
       </c>
       <c r="N101" t="str">
-        <v>[{"value":"true","valueLabel":"Yes"},{"value":"false","valueLabel":"No"}]</v>
+        <v>[{"value":"R","valueLabel":"Reactive"},{"value":"NR","valueLabel":"Non Reactive"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O101" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v>$NeoTreeOutcome = 'BID' and $MatHIVtest = true</v>
       </c>
       <c r="P101" t="str">
         <v/>
@@ -7297,13 +7297,13 @@
         <v>form</v>
       </c>
       <c r="F102" t="str">
-        <v>DateHIVtest</v>
+        <v>HAART</v>
       </c>
       <c r="G102" t="str">
-        <v>When was this test?</v>
+        <v>Mother on HAART?</v>
       </c>
       <c r="H102" t="str">
-        <v>date</v>
+        <v>dropdown</v>
       </c>
       <c r="I102" t="str">
         <v/>
@@ -7312,16 +7312,16 @@
         <v/>
       </c>
       <c r="K102" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="L102" t="str">
         <v>No</v>
       </c>
       <c r="M102" t="str">
-        <v/>
+        <v>$HIVtestResult = 'R' or $HIVtestResult = 'U'</v>
       </c>
       <c r="N102" t="str">
-        <v/>
+        <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"}]</v>
       </c>
       <c r="O102" t="str">
         <v>$NeoTreeOutcome = 'BID' and $MatHIVtest = true</v>
@@ -7365,10 +7365,10 @@
         <v>form</v>
       </c>
       <c r="F103" t="str">
-        <v>TestThisPreg</v>
+        <v>LengthHAART</v>
       </c>
       <c r="G103" t="str">
-        <v xml:space="preserve">Was the test during this pregnancy? </v>
+        <v>Mother on HAART since when?</v>
       </c>
       <c r="H103" t="str">
         <v>dropdown</v>
@@ -7386,10 +7386,10 @@
         <v>No</v>
       </c>
       <c r="M103" t="str">
-        <v/>
+        <v>$HAART = 'Y'</v>
       </c>
       <c r="N103" t="str">
-        <v>[{"value":"Y","valueLabel":"During this pregnancy"},{"value":"N","valueLabel":"Before this pregnancy"}]</v>
+        <v>[{"value":"1stTrim","valueLabel":"1st Trimester or earlier"},{"value":"2ndTrim","valueLabel":"2nd Trimester"},{"value":"3rdTrim","valueLabel":"3rd Trimester"}]</v>
       </c>
       <c r="O103" t="str">
         <v>$NeoTreeOutcome = 'BID' and $MatHIVtest = true</v>
@@ -7424,22 +7424,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C104" t="str">
-        <v>MATERNAL SEROSTATUS</v>
+        <v xml:space="preserve">MATERNAL SEROSTATUS </v>
       </c>
       <c r="D104" t="str">
-        <v xml:space="preserve">HIV TEST details </v>
+        <v>NVP</v>
       </c>
       <c r="E104" t="str">
-        <v>form</v>
+        <v>yesno</v>
       </c>
       <c r="F104" t="str">
-        <v>HIVtestResult</v>
+        <v>NVPgiven</v>
       </c>
       <c r="G104" t="str">
-        <v>What was the Result?</v>
+        <v>NVP given to baby</v>
       </c>
       <c r="H104" t="str">
-        <v>dropdown</v>
+        <v>boolean</v>
       </c>
       <c r="I104" t="str">
         <v/>
@@ -7448,19 +7448,19 @@
         <v/>
       </c>
       <c r="K104" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="L104" t="str">
         <v>No</v>
       </c>
       <c r="M104" t="str">
-        <v/>
+        <v>$HIVtestResult = 'R' or $HIVtestResult = 'U'</v>
       </c>
       <c r="N104" t="str">
-        <v>[{"value":"R","valueLabel":"Reactive"},{"value":"NR","valueLabel":"Non Reactive"},{"value":"U","valueLabel":"Unknown"}]</v>
+        <v>[{"value":"true","valueLabel":"Yes"},{"value":"false","valueLabel":"No"}]</v>
       </c>
       <c r="O104" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $MatHIVtest = true</v>
+        <v>$HIVtestResult = 'R' or $HIVtestResult = 'U'</v>
       </c>
       <c r="P104" t="str">
         <v/>
@@ -7492,22 +7492,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C105" t="str">
-        <v>MATERNAL SEROSTATUS</v>
+        <v>ANTENATAL HISTORY</v>
       </c>
       <c r="D105" t="str">
-        <v xml:space="preserve">HIV TEST details </v>
+        <v>Syphilis test</v>
       </c>
       <c r="E105" t="str">
-        <v>form</v>
+        <v>single_select</v>
       </c>
       <c r="F105" t="str">
-        <v>HAART</v>
+        <v>ANVDRL</v>
       </c>
       <c r="G105" t="str">
-        <v>Mother on HAART?</v>
+        <v>Syphilis test?</v>
       </c>
       <c r="H105" t="str">
-        <v>dropdown</v>
+        <v>single_select_option</v>
       </c>
       <c r="I105" t="str">
         <v/>
@@ -7516,19 +7516,19 @@
         <v/>
       </c>
       <c r="K105" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="L105" t="str">
         <v>No</v>
       </c>
       <c r="M105" t="str">
-        <v>$HIVtestResult = 'R' or $HIVtestResult = 'U'</v>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="N105" t="str">
-        <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"}]</v>
+        <v>[{"value":"Y","valueLabel":"YES","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"N","valueLabel":"NO","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"U","valueLabel":"NOT SURE","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O105" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $MatHIVtest = true</v>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="P105" t="str">
         <v/>
@@ -7560,19 +7560,19 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C106" t="str">
-        <v>MATERNAL SEROSTATUS</v>
+        <v xml:space="preserve">ANTENATAL HISTORY </v>
       </c>
       <c r="D106" t="str">
-        <v xml:space="preserve">HIV TEST details </v>
+        <v xml:space="preserve">VDRL details  </v>
       </c>
       <c r="E106" t="str">
         <v>form</v>
       </c>
       <c r="F106" t="str">
-        <v>LengthHAART</v>
+        <v>DateVDRLSameHIV</v>
       </c>
       <c r="G106" t="str">
-        <v>Mother on HAART since when?</v>
+        <v>Is Date of VDRL same as date of HIV test?</v>
       </c>
       <c r="H106" t="str">
         <v>dropdown</v>
@@ -7584,19 +7584,19 @@
         <v/>
       </c>
       <c r="K106" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="L106" t="str">
         <v>No</v>
       </c>
       <c r="M106" t="str">
-        <v>$HAART = 'Y'</v>
+        <v/>
       </c>
       <c r="N106" t="str">
-        <v>[{"value":"1stTrim","valueLabel":"1st Trimester or earlier"},{"value":"2ndTrim","valueLabel":"2nd Trimester"},{"value":"3rdTrim","valueLabel":"3rd Trimester"}]</v>
+        <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"}]</v>
       </c>
       <c r="O106" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $MatHIVtest = true</v>
+        <v>$ANVDRL = 'Y'</v>
       </c>
       <c r="P106" t="str">
         <v/>
@@ -7628,22 +7628,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C107" t="str">
-        <v xml:space="preserve">MATERNAL SEROSTATUS </v>
+        <v xml:space="preserve">ANTENATAL HISTORY </v>
       </c>
       <c r="D107" t="str">
-        <v>NVP</v>
+        <v xml:space="preserve">VDRL details  </v>
       </c>
       <c r="E107" t="str">
-        <v>yesno</v>
+        <v>form</v>
       </c>
       <c r="F107" t="str">
-        <v>NVPgiven</v>
+        <v>ANVDRLDate</v>
       </c>
       <c r="G107" t="str">
-        <v>NVP given to baby</v>
+        <v>Date of VDRL</v>
       </c>
       <c r="H107" t="str">
-        <v>boolean</v>
+        <v>date</v>
       </c>
       <c r="I107" t="str">
         <v/>
@@ -7658,13 +7658,13 @@
         <v>No</v>
       </c>
       <c r="M107" t="str">
-        <v>$HIVtestResult = 'R' or $HIVtestResult = 'U'</v>
+        <v>$DateVDRLSameHIV = 'N'</v>
       </c>
       <c r="N107" t="str">
-        <v>[{"value":"true","valueLabel":"Yes"},{"value":"false","valueLabel":"No"}]</v>
+        <v/>
       </c>
       <c r="O107" t="str">
-        <v>$HIVtestResult = 'R' or $HIVtestResult = 'U'</v>
+        <v>$ANVDRL = 'Y'</v>
       </c>
       <c r="P107" t="str">
         <v/>
@@ -7696,22 +7696,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C108" t="str">
-        <v>ANTENATAL HISTORY</v>
+        <v xml:space="preserve">ANTENATAL HISTORY </v>
       </c>
       <c r="D108" t="str">
-        <v>Syphilis test</v>
+        <v xml:space="preserve">VDRL details  </v>
       </c>
       <c r="E108" t="str">
-        <v>single_select</v>
+        <v>form</v>
       </c>
       <c r="F108" t="str">
-        <v>ANVDRL</v>
+        <v>ANVDRLResult</v>
       </c>
       <c r="G108" t="str">
-        <v>Syphilis test?</v>
+        <v>Result of VDRL</v>
       </c>
       <c r="H108" t="str">
-        <v>single_select_option</v>
+        <v>dropdown</v>
       </c>
       <c r="I108" t="str">
         <v/>
@@ -7726,13 +7726,13 @@
         <v>No</v>
       </c>
       <c r="M108" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v/>
       </c>
       <c r="N108" t="str">
-        <v>[{"value":"Y","valueLabel":"YES","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"N","valueLabel":"NO","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"U","valueLabel":"NOT SURE","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"P","valueLabel":"POSITIVE"},{"value":"N","valueLabel":"NEGATIVE"},{"value":"U","valueLabel":"UNKOWN"}]</v>
       </c>
       <c r="O108" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v>$ANVDRL = 'Y'</v>
       </c>
       <c r="P108" t="str">
         <v/>
@@ -7773,10 +7773,10 @@
         <v>form</v>
       </c>
       <c r="F109" t="str">
-        <v>DateVDRLSameHIV</v>
+        <v>ANMatSyphTreat</v>
       </c>
       <c r="G109" t="str">
-        <v>Is Date of VDRL same as date of HIV test?</v>
+        <v>COMPLETED treatment for syphilis antenatally?</v>
       </c>
       <c r="H109" t="str">
         <v>dropdown</v>
@@ -7794,7 +7794,7 @@
         <v>No</v>
       </c>
       <c r="M109" t="str">
-        <v/>
+        <v>$ANVDRLResult = 'P' or $ANVDRLResult = 'U'</v>
       </c>
       <c r="N109" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"}]</v>
@@ -7832,22 +7832,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C110" t="str">
-        <v xml:space="preserve">ANTENATAL HISTORY </v>
+        <v>ANTENATAL HISTORY</v>
       </c>
       <c r="D110" t="str">
-        <v xml:space="preserve">VDRL details  </v>
+        <v xml:space="preserve">Conditions </v>
       </c>
       <c r="E110" t="str">
-        <v>form</v>
+        <v>multi_select</v>
       </c>
       <c r="F110" t="str">
-        <v>ANVDRLDate</v>
+        <v>PregConditions</v>
       </c>
       <c r="G110" t="str">
-        <v>Date of VDRL</v>
+        <v>Medical conditions in pregnancy</v>
       </c>
       <c r="H110" t="str">
-        <v>date</v>
+        <v>multi_select_option</v>
       </c>
       <c r="I110" t="str">
         <v/>
@@ -7862,13 +7862,13 @@
         <v>No</v>
       </c>
       <c r="M110" t="str">
-        <v>$DateVDRLSameHIV = 'N'</v>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="N110" t="str">
-        <v/>
+        <v>[{"value":"HTN","valueLabel":"Hypertension or pre-eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DM","valueLabel":"Diabetes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MAL","valueLabel":"Malaria","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"STD","valueLabel":"Sexually Transmitted Disease (other than HIV/syphilis)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HD","valueLabel":"Heart disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"THY","valueLabel":"Thyroid disease / goitre","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AN","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O110" t="str">
-        <v>$ANVDRL = 'Y'</v>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="P110" t="str">
         <v/>
@@ -7900,22 +7900,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C111" t="str">
-        <v xml:space="preserve">ANTENATAL HISTORY </v>
+        <v>ANTENATAL HISTORY</v>
       </c>
       <c r="D111" t="str">
-        <v xml:space="preserve">VDRL details  </v>
+        <v>TypeSTD</v>
       </c>
       <c r="E111" t="str">
         <v>form</v>
       </c>
       <c r="F111" t="str">
-        <v>ANVDRLResult</v>
+        <v>TypeSTD</v>
       </c>
       <c r="G111" t="str">
-        <v>Result of VDRL</v>
+        <v>What was this STD?</v>
       </c>
       <c r="H111" t="str">
-        <v>dropdown</v>
+        <v>string</v>
       </c>
       <c r="I111" t="str">
         <v/>
@@ -7933,10 +7933,10 @@
         <v/>
       </c>
       <c r="N111" t="str">
-        <v>[{"value":"P","valueLabel":"POSITIVE"},{"value":"N","valueLabel":"NEGATIVE"},{"value":"U","valueLabel":"UNKOWN"}]</v>
+        <v/>
       </c>
       <c r="O111" t="str">
-        <v>$ANVDRL = 'Y'</v>
+        <v xml:space="preserve">$ANConditions = 'STD' </v>
       </c>
       <c r="P111" t="str">
         <v/>
@@ -7968,22 +7968,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C112" t="str">
-        <v xml:space="preserve">ANTENATAL HISTORY </v>
+        <v>ANTENATAL CARE</v>
       </c>
       <c r="D112" t="str">
-        <v xml:space="preserve">VDRL details  </v>
+        <v>ANC</v>
       </c>
       <c r="E112" t="str">
-        <v>form</v>
+        <v>single_select</v>
       </c>
       <c r="F112" t="str">
-        <v>ANMatSyphTreat</v>
+        <v>AntenatalCare</v>
       </c>
       <c r="G112" t="str">
-        <v>COMPLETED treatment for syphilis antenatally?</v>
+        <v>ANC visits</v>
       </c>
       <c r="H112" t="str">
-        <v>dropdown</v>
+        <v>single_select_option</v>
       </c>
       <c r="I112" t="str">
         <v/>
@@ -7998,13 +7998,13 @@
         <v>No</v>
       </c>
       <c r="M112" t="str">
-        <v>$ANVDRLResult = 'P' or $ANVDRLResult = 'U'</v>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="N112" t="str">
-        <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"}]</v>
+        <v>[{"value":"ANC0","valueLabel":"None","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ANC1","valueLabel":"1 ANC visit ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ANC2","valueLabel":"2 ANC visits","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ANC3","valueLabel":"3 ANC visits","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ANC4","valueLabel":"4 ANC visits","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ANC5orM","valueLabel":"More than 4 ANC visits","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ANCU","valueLabel":"Not sure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O112" t="str">
-        <v>$ANVDRL = 'Y'</v>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="P112" t="str">
         <v/>
@@ -8036,22 +8036,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C113" t="str">
-        <v>ANTENATAL HISTORY</v>
+        <v>ANTENATAL CARE</v>
       </c>
       <c r="D113" t="str">
-        <v xml:space="preserve">Conditions </v>
+        <v>IPT</v>
       </c>
       <c r="E113" t="str">
-        <v>multi_select</v>
+        <v>single_select</v>
       </c>
       <c r="F113" t="str">
-        <v>PregConditions</v>
+        <v>IPT</v>
       </c>
       <c r="G113" t="str">
-        <v>Medical conditions in pregnancy</v>
+        <v>IPT</v>
       </c>
       <c r="H113" t="str">
-        <v>multi_select_option</v>
+        <v>single_select_option</v>
       </c>
       <c r="I113" t="str">
         <v/>
@@ -8069,7 +8069,7 @@
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="N113" t="str">
-        <v>[{"value":"HTN","valueLabel":"Hypertension or pre-eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DM","valueLabel":"Diabetes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MAL","valueLabel":"Malaria","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"STD","valueLabel":"Sexually Transmitted Disease (other than HIV/syphilis)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HD","valueLabel":"Heart disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"THY","valueLabel":"Thyroid disease / goitre","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AN","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
+        <v>[{"value":"IPT0","valueLabel":"No SP doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPT1","valueLabel":"1 SP dose","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPT2","valueLabel":"2 SP doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPT3","valueLabel":"3 SP doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPT4","valueLabel":"4 SP doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPTU","valueLabel":"Not sure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O113" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -8104,22 +8104,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C114" t="str">
-        <v>ANTENATAL HISTORY</v>
+        <v>ANTENATAL CARE</v>
       </c>
       <c r="D114" t="str">
-        <v>TypeSTD</v>
+        <v>FeFo</v>
       </c>
       <c r="E114" t="str">
-        <v>form</v>
+        <v>single_select</v>
       </c>
       <c r="F114" t="str">
-        <v>TypeSTD</v>
+        <v>FeFo</v>
       </c>
       <c r="G114" t="str">
-        <v xml:space="preserve">What was this STD? </v>
+        <v>Iron &amp; Folate</v>
       </c>
       <c r="H114" t="str">
-        <v>string</v>
+        <v>single_select_option</v>
       </c>
       <c r="I114" t="str">
         <v/>
@@ -8134,13 +8134,13 @@
         <v>No</v>
       </c>
       <c r="M114" t="str">
-        <v/>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="N114" t="str">
-        <v/>
+        <v>[{"value":"Norm","valueLabel":"No FeFo given","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FeFo1","valueLabel":"Given FeFo x 1 ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FeFo2","valueLabel":"Given FeFo x 2 ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FeFo3","valueLabel":"Given FeFo x 3","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FeFo4","valueLabel":"Given FeFo x 4 ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FeFoU","valueLabel":"Not Sure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O114" t="str">
-        <v xml:space="preserve">$ANConditions = 'STD' </v>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="P114" t="str">
         <v/>
@@ -8175,16 +8175,16 @@
         <v>ANTENATAL CARE</v>
       </c>
       <c r="D115" t="str">
-        <v>ANC</v>
+        <v>TTV</v>
       </c>
       <c r="E115" t="str">
         <v>single_select</v>
       </c>
       <c r="F115" t="str">
-        <v>AntenatalCare</v>
+        <v>TTV</v>
       </c>
       <c r="G115" t="str">
-        <v xml:space="preserve">ANC visits </v>
+        <v>TTV</v>
       </c>
       <c r="H115" t="str">
         <v>single_select_option</v>
@@ -8205,7 +8205,7 @@
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="N115" t="str">
-        <v>[{"value":"ANC0","valueLabel":"None","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ANC1","valueLabel":"1 ANC visit ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ANC2","valueLabel":"2 ANC visits","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ANC3","valueLabel":"3 ANC visits","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ANC4","valueLabel":"4 ANC visits","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ANC5orM","valueLabel":"More than 4 ANC visits","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ANCU","valueLabel":"Not sure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"TTV0","valueLabel":"No TTV doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTV1","valueLabel":"1 TTV dose","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTV2","valueLabel":"2 TTV doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTV3 ","valueLabel":"3 TTV doses ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTVU","valueLabel":"Not sure ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O115" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -8243,16 +8243,16 @@
         <v>ANTENATAL CARE</v>
       </c>
       <c r="D116" t="str">
-        <v>IPT</v>
+        <v>Steroids</v>
       </c>
       <c r="E116" t="str">
         <v>single_select</v>
       </c>
       <c r="F116" t="str">
-        <v>IPT</v>
+        <v>ANSteroids</v>
       </c>
       <c r="G116" t="str">
-        <v>IPT</v>
+        <v>Antenatal steroids</v>
       </c>
       <c r="H116" t="str">
         <v>single_select_option</v>
@@ -8273,7 +8273,7 @@
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="N116" t="str">
-        <v>[{"value":"IPT0","valueLabel":"No SP doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPT1","valueLabel":"1 SP dose","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPT2","valueLabel":"2 SP doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPT3","valueLabel":"3 SP doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPT4","valueLabel":"4 SP doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPTU","valueLabel":"Not sure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"Y","valueLabel":"YES","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"N","valueLabel":"NO","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"U","valueLabel":"Not Sure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O116" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -8308,22 +8308,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C117" t="str">
-        <v>ANTENATAL CARE</v>
+        <v>LABOUR HISTORY</v>
       </c>
       <c r="D117" t="str">
-        <v>FeFo</v>
+        <v xml:space="preserve">Problems </v>
       </c>
       <c r="E117" t="str">
-        <v>single_select</v>
+        <v>multi_select</v>
       </c>
       <c r="F117" t="str">
-        <v>FeFo</v>
+        <v>ProbsLab</v>
       </c>
       <c r="G117" t="str">
-        <v xml:space="preserve">Iron &amp; Folate </v>
+        <v>Problems in Labour</v>
       </c>
       <c r="H117" t="str">
-        <v>single_select_option</v>
+        <v>multi_select_option</v>
       </c>
       <c r="I117" t="str">
         <v/>
@@ -8341,7 +8341,7 @@
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="N117" t="str">
-        <v>[{"value":"Norm","valueLabel":"No FeFo given","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FeFo1","valueLabel":"Given FeFo x 1 ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FeFo2","valueLabel":"Given FeFo x 2 ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FeFo3","valueLabel":"Given FeFo x 3","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FeFo4","valueLabel":"Given FeFo x 4 ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FeFoU","valueLabel":"Not Sure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"SVB","valueLabel":"Significant Vaginal Bleeding ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pre","valueLabel":"Pre-eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions / Eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Poly","valueLabel":"Polyhydramnios ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Olig","valueLabel":"Oligohydramnios","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O117" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -8376,22 +8376,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C118" t="str">
-        <v>ANTENATAL CARE</v>
+        <v xml:space="preserve">LABOUR HISTORY </v>
       </c>
       <c r="D118" t="str">
-        <v>TTV</v>
+        <v>Duration</v>
       </c>
       <c r="E118" t="str">
-        <v>single_select</v>
+        <v>form</v>
       </c>
       <c r="F118" t="str">
-        <v>TTV</v>
+        <v>DurationLab</v>
       </c>
       <c r="G118" t="str">
-        <v>TTV</v>
+        <v>Labour duration (Hrs)</v>
       </c>
       <c r="H118" t="str">
-        <v>single_select_option</v>
+        <v>number</v>
       </c>
       <c r="I118" t="str">
         <v/>
@@ -8406,10 +8406,10 @@
         <v>No</v>
       </c>
       <c r="M118" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v/>
       </c>
       <c r="N118" t="str">
-        <v>[{"value":"TTV0","valueLabel":"No TTV doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTV1","valueLabel":"1 TTV dose","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTV2","valueLabel":"2 TTV doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTV3 ","valueLabel":"3 TTV doses ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTVU","valueLabel":"Not sure ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v/>
       </c>
       <c r="O118" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -8444,22 +8444,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C119" t="str">
-        <v>ANTENATAL CARE</v>
+        <v xml:space="preserve">LABOUR HISTORY  </v>
       </c>
       <c r="D119" t="str">
-        <v>Steroids</v>
+        <v>ROM</v>
       </c>
       <c r="E119" t="str">
-        <v>single_select</v>
+        <v>form</v>
       </c>
       <c r="F119" t="str">
-        <v>ANSteroids</v>
+        <v>ROM</v>
       </c>
       <c r="G119" t="str">
-        <v>Antenatal steroids</v>
+        <v>Did the membranes rupture?</v>
       </c>
       <c r="H119" t="str">
-        <v>single_select_option</v>
+        <v>dropdown</v>
       </c>
       <c r="I119" t="str">
         <v/>
@@ -8474,10 +8474,10 @@
         <v>No</v>
       </c>
       <c r="M119" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v/>
       </c>
       <c r="N119" t="str">
-        <v>[{"value":"Y","valueLabel":"YES","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"N","valueLabel":"NO","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"U","valueLabel":"Not Sure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"}]</v>
       </c>
       <c r="O119" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -8512,22 +8512,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C120" t="str">
-        <v>LABOUR HISTORY</v>
+        <v xml:space="preserve">LABOUR HISTORY  </v>
       </c>
       <c r="D120" t="str">
-        <v xml:space="preserve">Problems </v>
+        <v>ROM</v>
       </c>
       <c r="E120" t="str">
-        <v>multi_select</v>
+        <v>form</v>
       </c>
       <c r="F120" t="str">
-        <v>ProbsLab</v>
+        <v>ROMLength</v>
       </c>
       <c r="G120" t="str">
-        <v xml:space="preserve">Problems in Labour </v>
+        <v>How long between ROM and birth?</v>
       </c>
       <c r="H120" t="str">
-        <v>multi_select_option</v>
+        <v>dropdown</v>
       </c>
       <c r="I120" t="str">
         <v/>
@@ -8542,10 +8542,10 @@
         <v>No</v>
       </c>
       <c r="M120" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v>$ROM = 'Y'</v>
       </c>
       <c r="N120" t="str">
-        <v>[{"value":"SVB","valueLabel":"Significant Vaginal Bleeding ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pre","valueLabel":"Pre-eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions / Eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Poly","valueLabel":"Polyhydramnios ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Olig","valueLabel":"Oligohydramnios","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
+        <v>[{"value":"NOPROM","valueLabel":"Less than 18 hours"},{"value":"PROM","valueLabel":"More than 18 hours"}]</v>
       </c>
       <c r="O120" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -8580,22 +8580,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C121" t="str">
-        <v xml:space="preserve">LABOUR HISTORY </v>
+        <v>Cause of brought in dead</v>
       </c>
       <c r="D121" t="str">
-        <v>Duration</v>
+        <v>Cause of BID</v>
       </c>
       <c r="E121" t="str">
         <v>form</v>
       </c>
       <c r="F121" t="str">
-        <v>DurationLab</v>
+        <v>CauseBID</v>
       </c>
       <c r="G121" t="str">
-        <v>Labour duration (Hrs)</v>
+        <v>Cause of BID</v>
       </c>
       <c r="H121" t="str">
-        <v>number</v>
+        <v>dropdown</v>
       </c>
       <c r="I121" t="str">
         <v/>
@@ -8613,7 +8613,7 @@
         <v/>
       </c>
       <c r="N121" t="str">
-        <v/>
+        <v>[{"value":"ME","valueLabel":"Maternal Eclampsia"},{"value":"EP","valueLabel":"Extreme Prematurity"},{"value":"ANH","valueLabel":"Antenatal Haemorrhage"},{"value":"PNH","valueLabel":"Postnatal Haemorrhage"},{"value":"O","valueLabel":"Other"}]</v>
       </c>
       <c r="O121" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -8648,22 +8648,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C122" t="str">
-        <v xml:space="preserve">LABOUR HISTORY  </v>
+        <v>Cause of brought in dead</v>
       </c>
       <c r="D122" t="str">
-        <v>ROM</v>
+        <v>Cause of BID</v>
       </c>
       <c r="E122" t="str">
         <v>form</v>
       </c>
       <c r="F122" t="str">
-        <v>ROM</v>
+        <v>CauseBIDOth</v>
       </c>
       <c r="G122" t="str">
-        <v>Did the membranes rupture?</v>
+        <v>If other what?</v>
       </c>
       <c r="H122" t="str">
-        <v>dropdown</v>
+        <v>string</v>
       </c>
       <c r="I122" t="str">
         <v/>
@@ -8678,10 +8678,10 @@
         <v>No</v>
       </c>
       <c r="M122" t="str">
-        <v/>
+        <v>$CauseBID = 'O'</v>
       </c>
       <c r="N122" t="str">
-        <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"}]</v>
+        <v/>
       </c>
       <c r="O122" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -8716,22 +8716,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C123" t="str">
-        <v xml:space="preserve">LABOUR HISTORY  </v>
+        <v>LABOUR HISTORY</v>
       </c>
       <c r="D123" t="str">
-        <v>ROM</v>
+        <v>RFSepsis</v>
       </c>
       <c r="E123" t="str">
-        <v>form</v>
+        <v>multi_select</v>
       </c>
       <c r="F123" t="str">
-        <v>ROMLength</v>
+        <v>RFSepsis</v>
       </c>
       <c r="G123" t="str">
-        <v>How long between ROM and birth?</v>
+        <v>Risk Factors for Sepsis</v>
       </c>
       <c r="H123" t="str">
-        <v>dropdown</v>
+        <v>multi_select_option</v>
       </c>
       <c r="I123" t="str">
         <v/>
@@ -8746,10 +8746,10 @@
         <v>No</v>
       </c>
       <c r="M123" t="str">
-        <v>$ROM = 'Y'</v>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="N123" t="str">
-        <v>[{"value":"NOPROM","valueLabel":"Less than 18 hours"},{"value":"PROM","valueLabel":"More than 18 hours"}]</v>
+        <v>[{"value":"PROM","valueLabel":"PROM more than 18 hrs","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MF","valueLabel":"Maternal fever in labour","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OL","valueLabel":"Offensive Liquor","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pr2nd","valueLabel":"Prolonged second stage","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival (BBA)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Prematurity &lt; 37 weeks","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O123" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -8784,19 +8784,19 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C124" t="str">
-        <v>Cause of brought in dead</v>
+        <v xml:space="preserve">BIRTH HISTORY </v>
       </c>
       <c r="D124" t="str">
-        <v>Cause of BID</v>
+        <v>Pres &amp; Deliv</v>
       </c>
       <c r="E124" t="str">
         <v>form</v>
       </c>
       <c r="F124" t="str">
-        <v>CauseBID</v>
+        <v>Presentation</v>
       </c>
       <c r="G124" t="str">
-        <v>Cause of BID</v>
+        <v>Presentation</v>
       </c>
       <c r="H124" t="str">
         <v>dropdown</v>
@@ -8814,10 +8814,10 @@
         <v>No</v>
       </c>
       <c r="M124" t="str">
-        <v/>
+        <v>$TypeBID != 'DU'</v>
       </c>
       <c r="N124" t="str">
-        <v>[{"value":"ME","valueLabel":"Maternal Eclampsia"},{"value":"EP","valueLabel":"Extreme Prematurity"},{"value":"ANH","valueLabel":"Antenatal Haemorrhage"},{"value":"PNH","valueLabel":"Postnatal Haemorrhage"},{"value":"O","valueLabel":"Other"}]</v>
+        <v>[{"value":"Vertex","valueLabel":"Vertex"},{"value":"Brow","valueLabel":"Brow"},{"value":"Breech","valueLabel":"Breech"},{"value":"Face","valueLabel":"Face"},{"value":"Unk","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O124" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -8852,22 +8852,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C125" t="str">
-        <v>Cause of brought in dead</v>
+        <v xml:space="preserve">BIRTH HISTORY </v>
       </c>
       <c r="D125" t="str">
-        <v>Cause of BID</v>
+        <v>Pres &amp; Deliv</v>
       </c>
       <c r="E125" t="str">
         <v>form</v>
       </c>
       <c r="F125" t="str">
-        <v>CauseBIDOth</v>
+        <v>ModeDelivery</v>
       </c>
       <c r="G125" t="str">
-        <v>If other what?</v>
+        <v>Mode of Delivery</v>
       </c>
       <c r="H125" t="str">
-        <v>string</v>
+        <v>dropdown</v>
       </c>
       <c r="I125" t="str">
         <v/>
@@ -8882,10 +8882,10 @@
         <v>No</v>
       </c>
       <c r="M125" t="str">
-        <v>$CauseBID = 'O'</v>
+        <v>$TypeBID != 'DU'</v>
       </c>
       <c r="N125" t="str">
-        <v/>
+        <v>[{"value":"1","valueLabel":"Spontaneous Vaginal Delivery (SVD)"},{"value":"2","valueLabel":"Vacuum extraction"},{"value":"3","valueLabel":"Forceps extraction"},{"value":"4","valueLabel":"Elective Ceasarian Section (ELCS)"},{"value":"5","valueLabel":"Emergency Ceasarian Section (EMCS)"},{"value":"6","valueLabel":"Breech extraction (vaginal)"},{"value":"7","valueLabel":"Induced Vaginal Delivery"}]</v>
       </c>
       <c r="O125" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -8920,22 +8920,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C126" t="str">
-        <v>LABOUR HISTORY</v>
+        <v xml:space="preserve">BIRTH HISTORY </v>
       </c>
       <c r="D126" t="str">
-        <v>RFSepsis</v>
+        <v>Pres &amp; Deliv</v>
       </c>
       <c r="E126" t="str">
-        <v>multi_select</v>
+        <v>form</v>
       </c>
       <c r="F126" t="str">
-        <v>RFSepsis</v>
+        <v>Reason</v>
       </c>
       <c r="G126" t="str">
-        <v xml:space="preserve">Risk Factors for Sepsis </v>
+        <v>Reason for CS:</v>
       </c>
       <c r="H126" t="str">
-        <v>multi_select_option</v>
+        <v>dropdown</v>
       </c>
       <c r="I126" t="str">
         <v/>
@@ -8950,10 +8950,10 @@
         <v>No</v>
       </c>
       <c r="M126" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v>$ModeDelivery = '4' or $ModeDelivery = '5'</v>
       </c>
       <c r="N126" t="str">
-        <v>[{"value":"PROM","valueLabel":"PROM more than 18 hrs","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MF","valueLabel":"Maternal fever in labour","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OL","valueLabel":"Offensive Liquor","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pr2nd","valueLabel":"Prolonged second stage","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival (BBA)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Prematurity &lt; 37 weeks","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
+        <v>[{"value":"FD","valueLabel":"Foetal Distress"},{"value":"Pres","valueLabel":"Malpresentation (e.g. breech)"},{"value":"Scar","valueLabel":"Previous scar(s)"},{"value":"E","valueLabel":"Eclampsia"},{"value":"PE","valueLabel":"Pre-Eclampsia"},{"value":"Fi","valueLabel":"Fibroids"},{"value":"Fund","valueLabel":"Big Fundus"},{"value":"Mult","valueLabel":"Multiple gestation"},{"value":"Pr","valueLabel":"Prolonged labour"},{"value":"Post","valueLabel":"Post Term"},{"value":"CPD","valueLabel":"Cephalopelvic Disproportion"},{"value":"O","valueLabel":"Other"}]</v>
       </c>
       <c r="O126" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -8997,13 +8997,13 @@
         <v>form</v>
       </c>
       <c r="F127" t="str">
-        <v>Presentation</v>
+        <v>ReasonOther</v>
       </c>
       <c r="G127" t="str">
-        <v>Presentation</v>
+        <v>Other Reason for CS</v>
       </c>
       <c r="H127" t="str">
-        <v>dropdown</v>
+        <v>string</v>
       </c>
       <c r="I127" t="str">
         <v/>
@@ -9018,10 +9018,10 @@
         <v>No</v>
       </c>
       <c r="M127" t="str">
-        <v>$TypeBID != 'DU'</v>
+        <v>($ModeDelivery = '4' or $ModeDelivery = '5') and $Reason = 'O'</v>
       </c>
       <c r="N127" t="str">
-        <v>[{"value":"Vertex","valueLabel":"Vertex"},{"value":"Brow","valueLabel":"Brow"},{"value":"Breech","valueLabel":"Breech"},{"value":"Face","valueLabel":"Face"},{"value":"Unk","valueLabel":"Unknown"}]</v>
+        <v/>
       </c>
       <c r="O127" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -9056,22 +9056,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C128" t="str">
-        <v xml:space="preserve">BIRTH HISTORY </v>
+        <v>BIRTH HISTORY</v>
       </c>
       <c r="D128" t="str">
-        <v>Pres &amp; Deliv</v>
+        <v>Meconium</v>
       </c>
       <c r="E128" t="str">
-        <v>form</v>
+        <v>single_select</v>
       </c>
       <c r="F128" t="str">
-        <v>ModeDelivery</v>
+        <v>MecPresent</v>
       </c>
       <c r="G128" t="str">
-        <v>Mode of Delivery</v>
+        <v>Meconium present?</v>
       </c>
       <c r="H128" t="str">
-        <v>dropdown</v>
+        <v>single_select_option</v>
       </c>
       <c r="I128" t="str">
         <v/>
@@ -9086,10 +9086,10 @@
         <v>No</v>
       </c>
       <c r="M128" t="str">
-        <v>$TypeBID != 'DU'</v>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="N128" t="str">
-        <v>[{"value":"1","valueLabel":"Spontaneous Vaginal Delivery (SVD)"},{"value":"2","valueLabel":"Vacuum extraction"},{"value":"3","valueLabel":"Forceps extraction"},{"value":"4","valueLabel":"Elective Ceasarian Section (ELCS)"},{"value":"5","valueLabel":"Emergency Ceasarian Section (EMCS)"},{"value":"6","valueLabel":"Breech extraction (vaginal)"},{"value":"7","valueLabel":"Induced Vaginal Delivery"}]</v>
+        <v>[{"value":"Yes","valueLabel":"Yes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"No","valueLabel":"No","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O128" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -9124,22 +9124,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C129" t="str">
-        <v xml:space="preserve">BIRTH HISTORY </v>
+        <v>BIRTH HISTORY</v>
       </c>
       <c r="D129" t="str">
-        <v>Pres &amp; Deliv</v>
+        <v>MecThick</v>
       </c>
       <c r="E129" t="str">
-        <v>form</v>
+        <v>single_select</v>
       </c>
       <c r="F129" t="str">
-        <v>Reason</v>
+        <v>MecThickThin</v>
       </c>
       <c r="G129" t="str">
-        <v>Reason for CS:</v>
+        <v>Thick / Thin</v>
       </c>
       <c r="H129" t="str">
-        <v>dropdown</v>
+        <v>single_select_option</v>
       </c>
       <c r="I129" t="str">
         <v/>
@@ -9154,13 +9154,13 @@
         <v>No</v>
       </c>
       <c r="M129" t="str">
-        <v>$ModeDelivery = '4' or $ModeDelivery = '5'</v>
+        <v xml:space="preserve">$MecPresent = 'Yes' </v>
       </c>
       <c r="N129" t="str">
-        <v>[{"value":"FD","valueLabel":"Foetal Distress"},{"value":"Pres","valueLabel":"Malpresentation (e.g. breech)"},{"value":"Scar","valueLabel":"Previous scar(s)"},{"value":"E","valueLabel":"Eclampsia"},{"value":"PE","valueLabel":"Pre-Eclampsia"},{"value":"Fi","valueLabel":"Fibroids"},{"value":"Fund","valueLabel":"Big Fundus"},{"value":"Mult","valueLabel":"Multiple gestation"},{"value":"Pr","valueLabel":"Prolonged labour"},{"value":"Post","valueLabel":"Post Term"},{"value":"CPD","valueLabel":"Cephalopelvic Disproportion"},{"value":"O","valueLabel":"Other"}]</v>
+        <v>[{"value":"Thick","valueLabel":"Thick","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Thin","valueLabel":"Thin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O129" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v xml:space="preserve">$MecPresent = 'Yes' </v>
       </c>
       <c r="P129" t="str">
         <v/>
@@ -9195,19 +9195,19 @@
         <v xml:space="preserve">BIRTH HISTORY </v>
       </c>
       <c r="D130" t="str">
-        <v>Pres &amp; Deliv</v>
+        <v>Apgars</v>
       </c>
       <c r="E130" t="str">
         <v>form</v>
       </c>
       <c r="F130" t="str">
-        <v>ReasonOther</v>
+        <v>CryBirth</v>
       </c>
       <c r="G130" t="str">
-        <v xml:space="preserve">Other Reason for CS </v>
+        <v>Did the baby cry straight after birth?</v>
       </c>
       <c r="H130" t="str">
-        <v>string</v>
+        <v>dropdown</v>
       </c>
       <c r="I130" t="str">
         <v/>
@@ -9222,10 +9222,10 @@
         <v>No</v>
       </c>
       <c r="M130" t="str">
-        <v>($ModeDelivery = '4' or $ModeDelivery = '5') and $Reason = 'O'</v>
+        <v/>
       </c>
       <c r="N130" t="str">
-        <v/>
+        <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O130" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -9260,22 +9260,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C131" t="str">
-        <v>BIRTH HISTORY</v>
+        <v xml:space="preserve">BIRTH HISTORY </v>
       </c>
       <c r="D131" t="str">
-        <v>Meconium</v>
+        <v>Apgars</v>
       </c>
       <c r="E131" t="str">
-        <v>single_select</v>
+        <v>form</v>
       </c>
       <c r="F131" t="str">
-        <v>MecPresent</v>
+        <v>Apgar1</v>
       </c>
       <c r="G131" t="str">
-        <v>Meconium present?</v>
+        <v>Apgar Score at 1 min</v>
       </c>
       <c r="H131" t="str">
-        <v>single_select_option</v>
+        <v>number</v>
       </c>
       <c r="I131" t="str">
         <v/>
@@ -9287,13 +9287,13 @@
         <v>No</v>
       </c>
       <c r="L131" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="M131" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v/>
       </c>
       <c r="N131" t="str">
-        <v>[{"value":"Yes","valueLabel":"Yes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"No","valueLabel":"No","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v/>
       </c>
       <c r="O131" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -9328,22 +9328,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C132" t="str">
-        <v>BIRTH HISTORY</v>
+        <v xml:space="preserve">BIRTH HISTORY </v>
       </c>
       <c r="D132" t="str">
-        <v>MecThick</v>
+        <v>Apgars</v>
       </c>
       <c r="E132" t="str">
-        <v>single_select</v>
+        <v>form</v>
       </c>
       <c r="F132" t="str">
-        <v>MecThickThin</v>
+        <v>Apgar5</v>
       </c>
       <c r="G132" t="str">
-        <v>Thick / Thin</v>
+        <v>Apgar Score at 5 min</v>
       </c>
       <c r="H132" t="str">
-        <v>single_select_option</v>
+        <v>number</v>
       </c>
       <c r="I132" t="str">
         <v/>
@@ -9355,16 +9355,16 @@
         <v>No</v>
       </c>
       <c r="L132" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="M132" t="str">
-        <v xml:space="preserve">$MecPresent = 'Yes' </v>
+        <v/>
       </c>
       <c r="N132" t="str">
-        <v>[{"value":"Thick","valueLabel":"Thick","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Thin","valueLabel":"Thin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v/>
       </c>
       <c r="O132" t="str">
-        <v xml:space="preserve">$MecPresent = 'Yes' </v>
+        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
       </c>
       <c r="P132" t="str">
         <v/>
@@ -9405,13 +9405,13 @@
         <v>form</v>
       </c>
       <c r="F133" t="str">
-        <v>CryBirth</v>
+        <v>Apgar10</v>
       </c>
       <c r="G133" t="str">
-        <v xml:space="preserve">Did the baby cry straight after birth? </v>
+        <v>Apgar Score at 10 min</v>
       </c>
       <c r="H133" t="str">
-        <v>dropdown</v>
+        <v>number</v>
       </c>
       <c r="I133" t="str">
         <v/>
@@ -9423,13 +9423,13 @@
         <v>No</v>
       </c>
       <c r="L133" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="M133" t="str">
         <v/>
       </c>
       <c r="N133" t="str">
-        <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
+        <v/>
       </c>
       <c r="O133" t="str">
         <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
@@ -9464,22 +9464,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C134" t="str">
-        <v xml:space="preserve">BIRTH HISTORY </v>
+        <v>BIRTH HISTORY</v>
       </c>
       <c r="D134" t="str">
-        <v>Apgars</v>
+        <v>Resus</v>
       </c>
       <c r="E134" t="str">
-        <v>form</v>
+        <v>multi_select</v>
       </c>
       <c r="F134" t="str">
-        <v>Apgar1</v>
+        <v>Resus</v>
       </c>
       <c r="G134" t="str">
-        <v xml:space="preserve">Apgar Score at 1 min </v>
+        <v>Resuscitation given</v>
       </c>
       <c r="H134" t="str">
-        <v>number</v>
+        <v>multi_select_option</v>
       </c>
       <c r="I134" t="str">
         <v/>
@@ -9491,16 +9491,16 @@
         <v>No</v>
       </c>
       <c r="L134" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M134" t="str">
-        <v/>
+        <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'ABS' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24' or $NeoTreeOutcome = 'DCR' or $NeoTreeOutcome = 'DPC'</v>
       </c>
       <c r="N134" t="str">
-        <v/>
+        <v>[{"value":"Stim","valueLabel":"Stimulation","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Suc","valueLabel":"Suctioning","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O2","valueLabel":"Oxygen","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BVM","valueLabel":"Bag Valve Mask Ventilation (BVM)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CPR","valueLabel":"Cardio Pulmonary Resuscitation (CPR)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O134" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'ABS' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24' or $NeoTreeOutcome = 'DCR' or $NeoTreeOutcome = 'DPC'</v>
       </c>
       <c r="P134" t="str">
         <v/>
@@ -9532,22 +9532,22 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C135" t="str">
-        <v xml:space="preserve">BIRTH HISTORY </v>
+        <v>BIRTH HISTORY</v>
       </c>
       <c r="D135" t="str">
-        <v>Apgars</v>
+        <v>Resus Length</v>
       </c>
       <c r="E135" t="str">
         <v>form</v>
       </c>
       <c r="F135" t="str">
-        <v>Apgar5</v>
+        <v>LengthResusKnown</v>
       </c>
       <c r="G135" t="str">
-        <v>Apgar Score at 5 min</v>
+        <v>Length of resuscitation known?</v>
       </c>
       <c r="H135" t="str">
-        <v>number</v>
+        <v>dropdown</v>
       </c>
       <c r="I135" t="str">
         <v/>
@@ -9559,16 +9559,16 @@
         <v>No</v>
       </c>
       <c r="L135" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M135" t="str">
         <v/>
       </c>
       <c r="N135" t="str">
-        <v/>
+        <v>[{"value":"Kn","valueLabel":"Known"},{"value":"Unk","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O135" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v>$Resus = 'O2' or $Resus = 'BVM' or $Resus = 'CPR'</v>
       </c>
       <c r="P135" t="str">
         <v/>
@@ -9600,19 +9600,19 @@
         <v>Kamuzu Central Hospital</v>
       </c>
       <c r="C136" t="str">
-        <v xml:space="preserve">BIRTH HISTORY </v>
+        <v>BIRTH HISTORY</v>
       </c>
       <c r="D136" t="str">
-        <v>Apgars</v>
+        <v>Resus Length</v>
       </c>
       <c r="E136" t="str">
         <v>form</v>
       </c>
       <c r="F136" t="str">
-        <v>Apgar10</v>
+        <v>LengthResus</v>
       </c>
       <c r="G136" t="str">
-        <v>Apgar Score at 10 min</v>
+        <v>Length of resus (min)</v>
       </c>
       <c r="H136" t="str">
         <v>number</v>
@@ -9627,16 +9627,16 @@
         <v>No</v>
       </c>
       <c r="L136" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M136" t="str">
-        <v/>
+        <v>$LengthResusKnown = 'Kn'</v>
       </c>
       <c r="N136" t="str">
         <v/>
       </c>
       <c r="O136" t="str">
-        <v>$NeoTreeOutcome = 'BID' and $TypeBID != 'DU'</v>
+        <v>$Resus = 'O2' or $Resus = 'BVM' or $Resus = 'CPR'</v>
       </c>
       <c r="P136" t="str">
         <v/>
@@ -10449,7 +10449,7 @@
         <v/>
       </c>
       <c r="N148" t="str">
-        <v>[{"value":"BDNY","valueLabel":"Bernadette Nyambo"},{"value":"BLPH","valueLabel":"Blessings Phiri"},{"value":"BRNA","valueLabel":"Bridget Namanya"},{"value":"DAMU","valueLabel":"Daniel Mughyombe"},{"value":"DRGZ","valueLabel":"Dr Gloria Zailani"},{"value":"DRMC","valueLabel":"Dr Msandeni Chume Kayuni"},{"value":"DRN","valueLabel":"Dr Noel"},{"value":"DRP","valueLabel":"Dr Priscilla"},{"value":"ELTE","valueLabel":"Elvin Tembo"},{"value":"EMMP","valueLabel":"Emily Mphonda"},{"value":"FEZA","valueLabel":"Fe Zambezi"},{"value":"FAST","valueLabel":"Fannie Steven"},{"value":"JEJE","valueLabel":"Jester Jere"},{"value":"LIPH","valueLabel":"Linna Phiri"},{"value":"MTKK","valueLabel":"Matron Kunkeyani"},{"value":"MPGR","valueLabel":"Mphatso Grant"},{"value":"NAME","valueLabel":"Naomie Meke"},{"value":"NAKH","valueLabel":"Naomie Khurungira"},{"value":"OMMA","valueLabel":"Omega Makonde"},{"value":"PECH","valueLabel":"Peter Chirwa"},{"value":"PRDI","valueLabel":"Precious Dinga"},{"value":"PRMA","valueLabel":"Prince Magawa"},{"value":"RHCH","valueLabel":"Rhoda Chifisi"},{"value":"RYAB","valueLabel":"Royce Abisai"},{"value":"TMNY","valueLabel":"Tamala Nyasulu"},{"value":"TAWH","valueLabel":"Tamandani Whayo"},{"value":"TCMD","valueLabel":"Tarcisious Maida"},{"value":"VEKU","valueLabel":"Veronica Kunkeyani"},{"value":"WAKU","valueLabel":"Watson Kumwenda"},{"value":"STU","valueLabel":"Student"},{"value":"OTH","valueLabel":"Other"}]</v>
+        <v>[{"value":"BDNY","valueLabel":"Bernadette Nyambo"},{"value":"BLPH","valueLabel":"Blessings Phiri"},{"value":"BRNA","valueLabel":"Bridget Namanya"},{"value":"DAMU","valueLabel":"Daniel Mughyombe"},{"value":"DRGZ","valueLabel":"Dr Gloria Zailani"},{"value":"DRMC","valueLabel":"Dr Msandeni Chume Kayuni"},{"value":"DRN","valueLabel":"Dr Noel"},{"value":"DRP","valueLabel":"Dr Priscilla"},{"value":"ELTE","valueLabel":"Elvin Tembo"},{"value":"EMMP","valueLabel":"Emily Mphonda"},{"value":"FEZA","valueLabel":"Fe Zambezi"},{"value":"FAST","valueLabel":"Fannie Steven"},{"value":"JEJE","valueLabel":"Jester Jere"},{"value":"LIPH","valueLabel":"Linna Phiri"},{"value":"MTKK","valueLabel":"Matron Kunkeyani"},{"value":"MPGR","valueLabel":"Mphatso Grant"},{"value":"NAME","valueLabel":"Naomie Meke"},{"value":"NAKH","valueLabel":"Naomie Khurungira"},{"value":"OMMA","valueLabel":"Omega Makonde"},{"value":"PECH","valueLabel":"Peter Chirwa"},{"value":"PRDI","valueLabel":"Precious Dinga"},{"value":"PRMA","valueLabel":"Prince Magawa"},{"value":"RHCH","valueLabel":"Rhoda Chifisi"},{"value":"RYAB","valueLabel":"Royce Abisai"},{"value":"TMNY","valueLabel":"Tamala Nyasulu"},{"value":"TAWH","valueLabel":"Tamandani Whayo"},{"value":"TCMD","valueLabel":"Tarcisious Maida"},{"value":"VEKU","valueLabel":"Veronica Kunkeyani"},{"value":"WAKU","valueLabel":"Watson Kumwenda"},{"value":"FNST","valueLabel":"Fannie Steven"},{"value":"TENJ","valueLabel":"Tendai Njeula"},{"value":"GLNK","valueLabel":"Gloria Nkhonjera"},{"value":"ELMU","valueLabel":"Eleanor Muhemera"},{"value":"NEKA","valueLabel":"Nenenji Kachiwiya"},{"value":"PENI","valueLabel":"Pemphero Nishiya"},{"value":"MENG","valueLabel":"Mercy Ngulume"},{"value":"DAKA","valueLabel":"Dalitso Kantwanje"},{"value":"CYMA","valueLabel":"Cynthia Matemba"},{"value":"TAWH","valueLabel":"Tamandani Whayo"},{"value":"EDCH","valueLabel":"Edith Chiwanda"},{"value":"LEKA","valueLabel":"Lexina Kamphanje"},{"value":"GEKO","valueLabel":"Getrude Kondwani"},{"value":"STU","valueLabel":"Student"},{"value":"OTH","valueLabel":"Other"}]</v>
       </c>
       <c r="O148" t="str">
         <v/>
